--- a/Thermomix TM6/Grading/1 stage/3-examples/Thermomix-TM6_Grading_1-stage_2026-02-28_3-examples_HumanGrading_Claude4.5SonnetGeneration.xlsx
+++ b/Thermomix TM6/Grading/1 stage/3-examples/Thermomix-TM6_Grading_1-stage_2026-02-28_3-examples_HumanGrading_Claude4.5SonnetGeneration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/Evaluations 2/Thermomix TM6/Grading/1 stage/2026-02-28/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Thermomix TM6/Grading/1 stage/3-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB264349-F460-784E-AF82-5A0C6E36713C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832F978F-AC50-7942-B719-C9FA8F28A73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thermonix" sheetId="1" r:id="rId1"/>
@@ -502,7 +502,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -751,24 +751,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -781,11 +763,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -929,19 +920,7 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -983,14 +962,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1346,24 +1334,40 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table_8" displayName="Table_8" ref="A1:D52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table_8" displayName="Table_8" ref="A1:D51">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Type"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Element"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Rater 1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Rater 2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Type">
+      <calculatedColumnFormula>Thermonix!A2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Element">
+      <calculatedColumnFormula>Thermonix!B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Rater 1">
+      <calculatedColumnFormula>'Thermonix Grader #1'!C2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Rater 2">
+      <calculatedColumnFormula>'Thermonix Grader #2'!C2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Inter-rater-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Table_9" displayName="Table_9" ref="A1:D52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Table_9" displayName="Table_9" ref="A1:D51">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Type"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Element"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Rater 1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Rater 2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Type">
+      <calculatedColumnFormula>Thermonix!A2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Element">
+      <calculatedColumnFormula>Thermonix!B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Rater 1">
+      <calculatedColumnFormula>'Thermonix Grader #1'!C2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Rater 2">
+      <calculatedColumnFormula>'Thermonix Grader #2'!C2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Weighted Cohens Kappa-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15380,16 +15384,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
       <c r="J1" s="30" t="s">
         <v>64</v>
       </c>
@@ -15711,16 +15715,16 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="78" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
+      <c r="B12" s="79"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="31" t="s">
@@ -17036,17 +17040,17 @@
       <c r="D1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="L1" s="81" t="s">
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="L1" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
     </row>
     <row r="2" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="str">
@@ -17112,15 +17116,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="45">
-        <f>COUNTIFS($C$2:$C$89, $F3, $D$2:$D$89, G$2)</f>
+        <f>COUNTIFS($C$2:$C$88, $F3, $D$2:$D$88, G$2)</f>
         <v>22</v>
       </c>
       <c r="H3" s="46">
-        <f>COUNTIFS($C$2:$C$45, $F3, $D$2:$D$45, H$2)</f>
+        <f>COUNTIFS($C$2:$C$44, $F3, $D$2:$D$44, H$2)</f>
         <v>0</v>
       </c>
       <c r="I3" s="47">
-        <f>COUNTIFS($C$2:$C$45, $F3, $D$2:$D$45, I$2)+MAX(D46-C46,0)+MAX(D47-C47,0)+MAX(D48-C48,0)+MAX(D49-C49,0)+MAX(D50-C50,0)+MAX(D51-C51,0)+MAX(D52-C52,0)</f>
+        <f>COUNTIFS($C$2:$C$44, $F3, $D$2:$D$44, I$2)+MAX(D45-C45,0)+MAX(D46-C46,0)+MAX(D47-C47,0)+MAX(D48-C48,0)+MAX(D49-C49,0)+MAX(D50-C50,0)+MAX(D51-C51,0)</f>
         <v>5</v>
       </c>
       <c r="J3" s="2">
@@ -17132,8 +17136,8 @@
         <v>90</v>
       </c>
       <c r="M3" s="45">
-        <f>(G3+H4+I5)/COUNTA($C$2:$C$99)</f>
-        <v>0.80392156862745101</v>
+        <f>(G3+H4+I5)/COUNTA($C$2:$C$98)</f>
+        <v>0.82</v>
       </c>
       <c r="N3" s="47" t="s">
         <v>91</v>
@@ -17160,28 +17164,28 @@
         <v>0.5</v>
       </c>
       <c r="G4" s="49">
-        <f t="shared" ref="G4:I4" si="1">COUNTIFS($C$2:$C$45, $F4, $D$2:$D$45, G$2)</f>
-        <v>0</v>
+        <f>COUNTIFS($C$2:$C$44, $F4, $D$2:$D$44, G$2)</f>
+        <v>1</v>
       </c>
       <c r="H4" s="2">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($C$2:$C$44, $F4, $D$2:$D$44, H$2)</f>
         <v>0</v>
       </c>
       <c r="I4" s="50">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($C$2:$C$44, $F4, $D$2:$D$44, I$2)</f>
         <v>0</v>
       </c>
       <c r="J4" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="48" t="s">
         <v>92</v>
       </c>
       <c r="M4" s="49">
-        <f t="array" ref="M4">SUMPRODUCT(J3:J5/COUNTA($C$2:$C$99), TRANSPOSE(G6:I6)/COUNTA($C$2:$C$99))</f>
-        <v>0.45213379469434833</v>
+        <f t="array" ref="M4">SUMPRODUCT(J3:J5/COUNTA($C$2:$C$98), TRANSPOSE(G6:I6)/COUNTA($C$2:$C$98))</f>
+        <v>0.48160000000000003</v>
       </c>
       <c r="N4" s="50" t="s">
         <v>93</v>
@@ -17208,15 +17212,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="51">
-        <f>COUNTIFS($C$2:$C$45, $F5, $D$2:$D$45, G$2)+MAX(C46-D46,0)+MAX(C47-D47,0)+MAX(C48-D48,0)+MAX(C49-D49,0)+MAX(C50-D50,0)+MAX(C51-D51,0)+MAX(C52-D52,0)</f>
+        <f>COUNTIFS($C$2:$C$44, $F5, $D$2:$D$44, G$2)+MAX(C45-D45,0)+MAX(C46-D46,0)+MAX(C47-D47,0)+MAX(C48-D48,0)+MAX(C49-D49,0)+MAX(C50-D50,0)+MAX(C51-D51,0)</f>
         <v>2</v>
       </c>
       <c r="H5" s="52">
-        <f>COUNTIFS($C$2:$C$45, $F5, $D$2:$D$45, H$2)</f>
+        <f>COUNTIFS($C$2:$C$44, $F5, $D$2:$D$44, H$2)</f>
         <v>1</v>
       </c>
       <c r="I5" s="53">
-        <f>COUNTIFS($C$2:$C$45, $F5, $D$2:$D$45, I$2)+ SUM(MIN(C46,D46), MIN(C47,D47), MIN(C48,D48), MIN(C49,D49), MIN(C50,D50), MIN(C51,D51), MIN(C52,D52))</f>
+        <f>COUNTIFS($C$2:$C$44, $F5, $D$2:$D$44, I$2)+ SUM(MIN(C45,D45), MIN(C46,D46), MIN(C47,D47), MIN(C48,D48), MIN(C49,D49), MIN(C50,D50), MIN(C51,D51))</f>
         <v>19</v>
       </c>
       <c r="J5" s="2">
@@ -17229,7 +17233,7 @@
       </c>
       <c r="M5" s="51">
         <f>(M3-M4)/(1-M4)</f>
-        <v>0.64210526315789473</v>
+        <v>0.65277777777777768</v>
       </c>
       <c r="N5" s="53" t="s">
         <v>94</v>
@@ -17256,15 +17260,15 @@
         <v>95</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" ref="G6:I6" si="2">SUM(G3:G5)</f>
-        <v>24</v>
+        <f t="shared" ref="G6:I6" si="1">SUM(G3:G5)</f>
+        <v>25</v>
       </c>
       <c r="H6" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I6" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="J6" s="2"/>
@@ -17309,17 +17313,17 @@
         <f>'Thermonix Grader #2'!C8</f>
         <v>1</v>
       </c>
-      <c r="F8" s="79" t="s">
+      <c r="F8" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="L8" s="81" t="s">
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="L8" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="M8" s="82"/>
-      <c r="N8" s="82"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="81"/>
     </row>
     <row r="9" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="str">
@@ -17385,19 +17389,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="45">
-        <f t="shared" ref="G10:H10" si="3">COUNTIFS($A$2:$A$89,$F$9,$C$2:$C$89,$F10,$D$2:$D$89,G$9)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$9,$C$2:$C$88,$F10,$D$2:$D$88,G$9)</f>
         <v>3</v>
       </c>
       <c r="H10" s="46">
-        <f t="shared" si="3"/>
+        <f>COUNTIFS($A$2:$A$88,$F$9,$C$2:$C$88,$F10,$D$2:$D$88,H$9)</f>
         <v>0</v>
       </c>
       <c r="I10" s="47">
-        <f t="shared" ref="I10:I11" si="4">COUNTIFS($A$2:$A$45,$F$9,$C$2:$C$45,$F10,$D$2:$D$45,I$9)+MAX(D46-C46,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$9,$C$2:$C$44,$F10,$D$2:$D$44,I$9)+MAX(D45-C45,0)</f>
         <v>1</v>
       </c>
       <c r="J10" s="2">
-        <f t="shared" ref="J10:J12" si="5">SUM(G10:I10)</f>
+        <f t="shared" ref="J10:J12" si="2">SUM(G10:I10)</f>
         <v>4</v>
       </c>
       <c r="K10" s="2"/>
@@ -17405,7 +17409,7 @@
         <v>90</v>
       </c>
       <c r="M10" s="45">
-        <f>(G10+H11+I12)/COUNTIF($A$2:$A$99,F9)</f>
+        <f>(G10+H11+I12)/COUNTIF($A$2:$A$98,F9)</f>
         <v>0.91666666666666663</v>
       </c>
       <c r="N10" s="47" t="s">
@@ -17433,19 +17437,19 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="45">
-        <f t="shared" ref="G11:H11" si="6">COUNTIFS($A$2:$A$89,$F$9,$C$2:$C$89,$F11,$D$2:$D$89,G$9)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$9,$C$2:$C$88,$F11,$D$2:$D$88,G$9)</f>
         <v>0</v>
       </c>
       <c r="H11" s="46">
-        <f t="shared" si="6"/>
+        <f>COUNTIFS($A$2:$A$88,$F$9,$C$2:$C$88,$F11,$D$2:$D$88,H$9)</f>
         <v>0</v>
       </c>
       <c r="I11" s="47">
-        <f t="shared" si="4"/>
+        <f>COUNTIFS($A$2:$A$44,$F$9,$C$2:$C$44,$F11,$D$2:$D$44,I$9)+MAX(D46-C46,0)</f>
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K11" s="2"/>
@@ -17453,8 +17457,8 @@
         <v>92</v>
       </c>
       <c r="M11" s="49">
-        <f t="array" ref="M11">SUMPRODUCT(J10:J12/COUNTA($C$2:$C$99), TRANSPOSE(G13:I13)/COUNTA($C$2:$C$99))</f>
-        <v>3.2295271049596314E-2</v>
+        <f t="array" ref="M11">SUMPRODUCT(J10:J12/COUNTA($C$2:$C$98), TRANSPOSE(G13:I13)/COUNTA($C$2:$C$98))</f>
+        <v>3.3599999999999998E-2</v>
       </c>
       <c r="N11" s="50"/>
     </row>
@@ -17479,19 +17483,19 @@
         <v>1</v>
       </c>
       <c r="G12" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$9,$C$2:$C$45,$F12,$D$2:$D$45,G$9)+MAX(C46-D46,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$9,$C$2:$C$44,$F12,$D$2:$D$44,G$9)+MAX(C45-D45,0)</f>
         <v>0</v>
       </c>
       <c r="H12" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$9,$C$2:$C$89,$F12,$D$2:$D$89,H$9)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$9,$C$2:$C$88,$F12,$D$2:$D$88,H$9)</f>
         <v>0</v>
       </c>
       <c r="I12" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$9,$C$2:$C$45,$F12,$D$2:$D$45,I$9)+MIN(C46-D46)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$9,$C$2:$C$44,$F12,$D$2:$D$44,I$9)+MIN(C45-D45)</f>
         <v>8</v>
       </c>
       <c r="J12" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="L12" s="48" t="s">
@@ -17499,7 +17503,7 @@
       </c>
       <c r="M12" s="51">
         <f>(M3-M4)/(1-M4)</f>
-        <v>0.64210526315789473</v>
+        <v>0.65277777777777768</v>
       </c>
       <c r="N12" s="53" t="s">
         <v>94</v>
@@ -17526,15 +17530,15 @@
         <v>95</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" ref="G13:I13" si="7">SUM(G10:G12)</f>
+        <f t="shared" ref="G13:I13" si="3">SUM(G10:G12)</f>
         <v>3</v>
       </c>
       <c r="H13" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="J13" s="2"/>
@@ -17576,18 +17580,18 @@
         <f>'Thermonix Grader #2'!C15</f>
         <v>1</v>
       </c>
-      <c r="F15" s="79" t="s">
+      <c r="F15" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="81" t="s">
+      <c r="L15" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="M15" s="82"/>
-      <c r="N15" s="82"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="81"/>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="str">
@@ -17660,19 +17664,19 @@
         <v>0</v>
       </c>
       <c r="G17" s="45">
-        <f t="shared" ref="G17:H17" si="8">COUNTIFS($A$2:$A$89,$F$16,$C$2:$C$89,$F17,$D$2:$D$89,G$16)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F17,$D$2:$D$88,G$16)</f>
         <v>6</v>
       </c>
       <c r="H17" s="46">
-        <f t="shared" si="8"/>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F17,$D$2:$D$88,H$16)</f>
         <v>0</v>
       </c>
       <c r="I17" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$16,$C$2:$C$45,$F17,$D$2:$D$45,I$16) + MAX(D47-C47,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$16,$C$2:$C$44,$F17,$D$2:$D$44,I$16) + MAX(D46-C46,0)</f>
         <v>3</v>
       </c>
       <c r="J17" s="2">
-        <f t="shared" ref="J17:J19" si="9">SUM(G17:I17)</f>
+        <f t="shared" ref="J17:J19" si="4">SUM(G17:I17)</f>
         <v>9</v>
       </c>
       <c r="K17" s="2"/>
@@ -17680,7 +17684,7 @@
         <v>90</v>
       </c>
       <c r="M17" s="45">
-        <f>(G17+H18+I19)/COUNTIF($A$2:$A$99,F16)</f>
+        <f>(G17+H18+I19)/COUNTIF($A$2:$A$98,F16)</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="N17" s="47" t="s">
@@ -17708,19 +17712,19 @@
         <v>0.5</v>
       </c>
       <c r="G18" s="49">
-        <f t="shared" ref="G18:I18" si="10">COUNTIFS($A$2:$A$89,$F$16,$C$2:$C$89,$F18,$D$2:$D$89,G$16)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F18,$D$2:$D$88,G$16)</f>
         <v>0</v>
       </c>
       <c r="H18" s="2">
-        <f t="shared" si="10"/>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F18,$D$2:$D$88,H$16)</f>
         <v>0</v>
       </c>
       <c r="I18" s="50">
-        <f t="shared" si="10"/>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F18,$D$2:$D$88,I$16)</f>
         <v>0</v>
       </c>
       <c r="J18" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K18" s="2"/>
@@ -17728,7 +17732,7 @@
         <v>92</v>
       </c>
       <c r="M18" s="49">
-        <f t="array" ref="M18">SUMPRODUCT(J17:J19/COUNTIF($A$2:$A$99,F16), TRANSPOSE(G20:I20)/COUNTIF($A$2:$A$99,F16))</f>
+        <f t="array" ref="M18">SUMPRODUCT(J17:J19/COUNTIF($A$2:$A$98,F16), TRANSPOSE(G20:I20)/COUNTIF($A$2:$A$98,F16))</f>
         <v>0.5</v>
       </c>
       <c r="N18" s="50" t="s">
@@ -17756,19 +17760,19 @@
         <v>1</v>
       </c>
       <c r="G19" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$16,$C$2:$C$45,$F19,$D$2:$D$45,G$16)+MAX(C47-D47,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$16,$C$2:$C$44,$F19,$D$2:$D$44,G$16)+MAX(C46-D46,0)</f>
         <v>0</v>
       </c>
       <c r="H19" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$16,$C$2:$C$89,$F19,$D$2:$D$89,H$16)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F19,$D$2:$D$88,H$16)</f>
         <v>0</v>
       </c>
       <c r="I19" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$16,$C$2:$C$45,$F19,$D$2:$D$45,I$16) + MIN(C47,D47)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$16,$C$2:$C$44,$F19,$D$2:$D$44,I$16) + MIN(C46,D46)</f>
         <v>9</v>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="L19" s="48" t="s">
@@ -17803,15 +17807,15 @@
         <v>95</v>
       </c>
       <c r="G20" s="2">
-        <f t="shared" ref="G20:I20" si="11">SUM(G17:G19)</f>
+        <f t="shared" ref="G20:I20" si="5">SUM(G17:G19)</f>
         <v>6</v>
       </c>
       <c r="H20" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="J20" s="2"/>
@@ -17854,18 +17858,18 @@
         <v>1</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="79" t="s">
+      <c r="F22" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
       <c r="K22" s="2"/>
-      <c r="L22" s="81" t="s">
+      <c r="L22" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="M22" s="82"/>
-      <c r="N22" s="82"/>
+      <c r="M22" s="81"/>
+      <c r="N22" s="81"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
@@ -17937,19 +17941,19 @@
         <v>0</v>
       </c>
       <c r="G24" s="45">
-        <f t="shared" ref="G24:H24" si="12">COUNTIFS($A$2:$A$89,$F$23,$C$2:$C$89,$F24,$D$2:$D$89,G$23)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F24,$D$2:$D$88,G$23)</f>
         <v>1</v>
       </c>
       <c r="H24" s="46">
-        <f t="shared" si="12"/>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F24,$D$2:$D$88,H$23)</f>
         <v>0</v>
       </c>
       <c r="I24" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$23,$C$2:$C$45,$F24,$D$2:$D$45,I$23) + MAX(D50-C50,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$23,$C$2:$C$44,$F24,$D$2:$D$44,I$23) + MAX(D49-C49,0)</f>
         <v>0</v>
       </c>
       <c r="J24" s="2">
-        <f t="shared" ref="J24:J26" si="13">SUM(G24:I24)</f>
+        <f t="shared" ref="J24:J26" si="6">SUM(G24:I24)</f>
         <v>1</v>
       </c>
       <c r="K24" s="2"/>
@@ -17957,7 +17961,7 @@
         <v>90</v>
       </c>
       <c r="M24" s="45">
-        <f>(G24+H25+I26)/COUNTIF($A$2:$A$99,F23)</f>
+        <f>(G24+H25+I26)/COUNTIF($A$2:$A$98,F23)</f>
         <v>1</v>
       </c>
       <c r="N24" s="47" t="s">
@@ -17977,27 +17981,27 @@
         <f>'Thermonix Grader #1'!C25</f>
         <v>0.5</v>
       </c>
-      <c r="D25" s="25" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="D25" s="25">
+        <f>'Thermonix Grader #2'!C25</f>
+        <v>0</v>
       </c>
       <c r="F25" s="44">
         <v>0.5</v>
       </c>
       <c r="G25" s="49">
-        <f t="shared" ref="G25:I25" si="14">COUNTIFS($A$2:$A$89,$F$23,$C$2:$C$89,$F25,$D$2:$D$89,G$23)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F25,$D$2:$D$88,G$23)</f>
         <v>0</v>
       </c>
       <c r="H25" s="2">
-        <f t="shared" si="14"/>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F25,$D$2:$D$88,H$23)</f>
         <v>0</v>
       </c>
       <c r="I25" s="50">
-        <f t="shared" si="14"/>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F25,$D$2:$D$88,I$23)</f>
         <v>0</v>
       </c>
       <c r="J25" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K25" s="2"/>
@@ -18005,7 +18009,7 @@
         <v>92</v>
       </c>
       <c r="M25" s="49">
-        <f t="array" ref="M25">SUMPRODUCT(J24:J26/COUNTIF($A$2:$A$99,F23), TRANSPOSE(G27:I27)/COUNTIF($A$2:$A$99,F23))</f>
+        <f t="array" ref="M25">SUMPRODUCT(J24:J26/COUNTIF($A$2:$A$98,F23), TRANSPOSE(G27:I27)/COUNTIF($A$2:$A$98,F23))</f>
         <v>0.5</v>
       </c>
       <c r="N25" s="50" t="s">
@@ -18013,39 +18017,39 @@
       </c>
     </row>
     <row r="26" spans="1:20" ht="13" x14ac:dyDescent="0.15">
-      <c r="A26" s="3" t="e">
-        <f t="shared" ref="A26:C26" si="15">#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B26" s="4" t="e">
-        <f t="shared" si="15"/>
-        <v>#REF!</v>
-      </c>
-      <c r="C26" s="25" t="e">
-        <f t="shared" si="15"/>
-        <v>#REF!</v>
+      <c r="A26" s="3" t="str">
+        <f>Thermonix!A26</f>
+        <v>Action</v>
+      </c>
+      <c r="B26" s="4" t="str">
+        <f>Thermonix!B26</f>
+        <v>setIngredients()</v>
+      </c>
+      <c r="C26" s="25">
+        <f>'Thermonix Grader #1'!C26</f>
+        <v>0</v>
       </c>
       <c r="D26" s="25">
-        <f>'Thermonix Grader #2'!C25</f>
+        <f>'Thermonix Grader #2'!C26</f>
         <v>0</v>
       </c>
       <c r="F26" s="44">
         <v>1</v>
       </c>
       <c r="G26" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$23,$C$2:$C$45,$F26,$D$2:$D$45,G$23) + MAX(C50-D50,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$23,$C$2:$C$44,$F26,$D$2:$D$44,G$23) + MAX(C49-D49,0)</f>
         <v>0</v>
       </c>
       <c r="H26" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$23,$C$2:$C$89,$F26,$D$2:$D$89,H$23)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F26,$D$2:$D$88,H$23)</f>
         <v>0</v>
       </c>
       <c r="I26" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$23,$C$2:$C$45,$F26,$D$2:$D$45,I$23) + MIN(C50,D50)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$23,$C$2:$C$44,$F26,$D$2:$D$44,I$23) + MIN(C49,D49)</f>
         <v>1</v>
       </c>
       <c r="J26" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L26" s="48" t="s">
@@ -18061,34 +18065,34 @@
     </row>
     <row r="27" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="str">
-        <f>Thermonix!A26</f>
-        <v>Action</v>
+        <f>Thermonix!A27</f>
+        <v>Transition</v>
       </c>
       <c r="B27" s="4" t="str">
-        <f>Thermonix!B26</f>
-        <v>setIngredients()</v>
+        <f>Thermonix!B27</f>
+        <v>next (PromptToAdd ⇒ Chop)</v>
       </c>
       <c r="C27" s="25">
-        <f>'Thermonix Grader #1'!C26</f>
+        <f>'Thermonix Grader #1'!C27</f>
         <v>0</v>
       </c>
       <c r="D27" s="25">
-        <f>'Thermonix Grader #2'!C26</f>
-        <v>0</v>
+        <f>'Thermonix Grader #2'!C27</f>
+        <v>1</v>
       </c>
       <c r="F27" s="54" t="s">
         <v>95</v>
       </c>
       <c r="G27" s="2">
-        <f t="shared" ref="G27:I27" si="16">SUM(G24:G26)</f>
+        <f t="shared" ref="G27:I27" si="7">SUM(G24:G26)</f>
         <v>1</v>
       </c>
       <c r="H27" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J27" s="2"/>
@@ -18097,68 +18101,68 @@
     </row>
     <row r="28" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="str">
-        <f>Thermonix!A27</f>
-        <v>Transition</v>
+        <f>Thermonix!A28</f>
+        <v>Guard</v>
       </c>
       <c r="B28" s="4" t="str">
-        <f>Thermonix!B27</f>
-        <v>next (PromptToAdd ⇒ Chop)</v>
+        <f>Thermonix!B28</f>
+        <v>[weightCorrect() &amp;&amp; !moreIngredientsRequired()]</v>
       </c>
       <c r="C28" s="25">
-        <f>'Thermonix Grader #1'!C27</f>
+        <f>'Thermonix Grader #1'!C28</f>
         <v>0</v>
       </c>
       <c r="D28" s="25">
-        <f>'Thermonix Grader #2'!C27</f>
+        <f>'Thermonix Grader #2'!C28</f>
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="str">
-        <f>Thermonix!A28</f>
-        <v>Guard</v>
+        <f>Thermonix!A29</f>
+        <v>Action</v>
       </c>
       <c r="B29" s="4" t="str">
-        <f>Thermonix!B28</f>
-        <v>[weightCorrect() &amp;&amp; !moreIngredientsRequired()]</v>
+        <f>Thermonix!B29</f>
+        <v>setChoppingSpeedAndTime()</v>
       </c>
       <c r="C29" s="25">
-        <f>'Thermonix Grader #1'!C28</f>
-        <v>0</v>
+        <f>'Thermonix Grader #1'!C29</f>
+        <v>1</v>
       </c>
       <c r="D29" s="25">
-        <f>'Thermonix Grader #2'!C28</f>
-        <v>1</v>
-      </c>
-      <c r="F29" s="79" t="s">
+        <f>'Thermonix Grader #2'!C29</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="G29" s="80"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="81" t="s">
+      <c r="L29" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="M29" s="82"/>
-      <c r="N29" s="82"/>
+      <c r="M29" s="81"/>
+      <c r="N29" s="81"/>
     </row>
     <row r="30" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="str">
-        <f>Thermonix!A29</f>
-        <v>Action</v>
+        <f>Thermonix!A30</f>
+        <v>State</v>
       </c>
       <c r="B30" s="4" t="str">
-        <f>Thermonix!B29</f>
-        <v>setChoppingSpeedAndTime()</v>
+        <f>Thermonix!B30</f>
+        <v>Chop</v>
       </c>
       <c r="C30" s="25">
-        <f>'Thermonix Grader #1'!C29</f>
+        <f>'Thermonix Grader #1'!C30</f>
         <v>1</v>
       </c>
       <c r="D30" s="25">
-        <f>'Thermonix Grader #2'!C29</f>
-        <v>0</v>
+        <f>'Thermonix Grader #2'!C30</f>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>22</v>
@@ -18188,38 +18192,38 @@
     </row>
     <row r="31" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="str">
-        <f>Thermonix!A30</f>
-        <v>State</v>
+        <f>Thermonix!A31</f>
+        <v>Transition</v>
       </c>
       <c r="B31" s="4" t="str">
-        <f>Thermonix!B30</f>
-        <v>Chop</v>
+        <f>Thermonix!B31</f>
+        <v>next (Chop ⇒ PromptToAdd)</v>
       </c>
       <c r="C31" s="25">
-        <f>'Thermonix Grader #1'!C30</f>
-        <v>1</v>
+        <f>'Thermonix Grader #1'!C31</f>
+        <v>0</v>
       </c>
       <c r="D31" s="25">
-        <f>'Thermonix Grader #2'!C30</f>
-        <v>1</v>
+        <f>'Thermonix Grader #2'!C31</f>
+        <v>0</v>
       </c>
       <c r="F31" s="44">
         <v>0</v>
       </c>
       <c r="G31" s="45">
-        <f t="shared" ref="G31:H31" si="17">COUNTIFS($A$2:$A$89,$F$30,$C$2:$C$89,$F31,$D$2:$D$89,G$30)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F31,$D$2:$D$88,G$30)</f>
         <v>4</v>
       </c>
       <c r="H31" s="46">
-        <f t="shared" si="17"/>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F31,$D$2:$D$88,H$30)</f>
         <v>0</v>
       </c>
       <c r="I31" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$30,$C$2:$C$45,$F31,$D$2:$D$45,I$30) + MAX(D48-C48,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$30,$C$2:$C$44,$F31,$D$2:$D$44,I$30) + MAX(D47-C47,0)</f>
         <v>1</v>
       </c>
       <c r="J31" s="2">
-        <f t="shared" ref="J31:J33" si="18">SUM(G31:I31)</f>
+        <f t="shared" ref="J31:J33" si="8">SUM(G31:I31)</f>
         <v>5</v>
       </c>
       <c r="K31" s="2"/>
@@ -18227,7 +18231,7 @@
         <v>90</v>
       </c>
       <c r="M31" s="45">
-        <f>(G31+H32+I33)/COUNTIF($A$2:$A$99,F30)</f>
+        <f>(G31+H32+I33)/COUNTIF($A$2:$A$98,F30)</f>
         <v>0.625</v>
       </c>
       <c r="N31" s="47" t="s">
@@ -18236,47 +18240,47 @@
     </row>
     <row r="32" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="str">
-        <f>Thermonix!A31</f>
-        <v>Transition</v>
+        <f>Thermonix!A32</f>
+        <v>Guard</v>
       </c>
       <c r="B32" s="4" t="str">
-        <f>Thermonix!B31</f>
-        <v>next (Chop ⇒ PromptToAdd)</v>
+        <f>Thermonix!B32</f>
+        <v>[choppingTimeDone &amp;&amp; moreIngredientsRequired()]</v>
       </c>
       <c r="C32" s="25">
-        <f>'Thermonix Grader #1'!C31</f>
+        <f>'Thermonix Grader #1'!C32</f>
         <v>0</v>
       </c>
       <c r="D32" s="25">
-        <f>'Thermonix Grader #2'!C31</f>
+        <f>'Thermonix Grader #2'!C32</f>
         <v>0</v>
       </c>
       <c r="F32" s="44">
         <v>0.5</v>
       </c>
       <c r="G32" s="49">
-        <f t="shared" ref="G32:I32" si="19">COUNTIFS($A$2:$A$89,$F$30,$C$2:$C$89,$F32,$D$2:$D$89,G$30)</f>
-        <v>0</v>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F32,$D$2:$D$88,G$30)</f>
+        <v>1</v>
       </c>
       <c r="H32" s="2">
-        <f t="shared" si="19"/>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F32,$D$2:$D$88,H$30)</f>
         <v>0</v>
       </c>
       <c r="I32" s="50">
-        <f t="shared" si="19"/>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F32,$D$2:$D$88,I$30)</f>
         <v>0</v>
       </c>
       <c r="J32" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="48" t="s">
         <v>92</v>
       </c>
       <c r="M32" s="49">
-        <f t="array" ref="M32">SUMPRODUCT(J31:J33/COUNTIF($A$2:$A$99,F30), TRANSPOSE(G34:I34)/COUNTIF($A$2:$A$99,F30))</f>
-        <v>0.375</v>
+        <f t="array" ref="M32">SUMPRODUCT(J31:J33/COUNTIF($A$2:$A$98,F30), TRANSPOSE(G34:I34)/COUNTIF($A$2:$A$98,F30))</f>
+        <v>0.46875</v>
       </c>
       <c r="N32" s="50" t="s">
         <v>93</v>
@@ -18284,38 +18288,38 @@
     </row>
     <row r="33" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="str">
-        <f>Thermonix!A32</f>
-        <v>Guard</v>
+        <f>Thermonix!A33</f>
+        <v>Action</v>
       </c>
       <c r="B33" s="4" t="str">
-        <f>Thermonix!B32</f>
-        <v>[choppingTimeDone &amp;&amp; moreIngredientsRequired()]</v>
+        <f>Thermonix!B33</f>
+        <v>setIngredients()</v>
       </c>
       <c r="C33" s="25">
-        <f>'Thermonix Grader #1'!C32</f>
+        <f>'Thermonix Grader #1'!C33</f>
         <v>0</v>
       </c>
       <c r="D33" s="25">
-        <f>'Thermonix Grader #2'!C32</f>
+        <f>'Thermonix Grader #2'!C33</f>
         <v>0</v>
       </c>
       <c r="F33" s="44">
         <v>1</v>
       </c>
       <c r="G33" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$30,$C$2:$C$45,$F33,$D$2:$D$45,G$30) + MAX(C48-D48,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$30,$C$2:$C$44,$F33,$D$2:$D$44,G$30) + MAX(C47-D47,0)</f>
         <v>0</v>
       </c>
       <c r="H33" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$30,$C$2:$C$89,$F33,$D$2:$D$89,H$30)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F33,$D$2:$D$88,H$30)</f>
         <v>1</v>
       </c>
       <c r="I33" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$30,$C$2:$C$45,$F33,$D$2:$D$45,I$30) + MIN(C48,D48)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$30,$C$2:$C$44,$F33,$D$2:$D$44,I$30) + MIN(C47,D47)</f>
         <v>1</v>
       </c>
       <c r="J33" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="L33" s="48" t="s">
@@ -18323,7 +18327,7 @@
       </c>
       <c r="M33" s="51">
         <f>(M31-M32)/(1-M32)</f>
-        <v>0.4</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="N33" s="53" t="s">
         <v>94</v>
@@ -18331,35 +18335,35 @@
     </row>
     <row r="34" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="str">
-        <f>Thermonix!A33</f>
-        <v>Action</v>
+        <f>Thermonix!A34</f>
+        <v>Transition</v>
       </c>
       <c r="B34" s="4" t="str">
-        <f>Thermonix!B33</f>
-        <v>setIngredients()</v>
+        <f>Thermonix!B34</f>
+        <v>next (Chop ⇒ Cook)</v>
       </c>
       <c r="C34" s="25">
-        <f>'Thermonix Grader #1'!C33</f>
-        <v>0</v>
+        <f>'Thermonix Grader #1'!C34</f>
+        <v>1</v>
       </c>
       <c r="D34" s="25">
-        <f>'Thermonix Grader #2'!C33</f>
-        <v>0</v>
+        <f>'Thermonix Grader #2'!C34</f>
+        <v>1</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="54" t="s">
         <v>95</v>
       </c>
       <c r="G34" s="2">
-        <f t="shared" ref="G34:I34" si="20">SUM(G31:G33)</f>
-        <v>4</v>
+        <f t="shared" ref="G34:I34" si="9">SUM(G31:G33)</f>
+        <v>5</v>
       </c>
       <c r="H34" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="I34" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="J34" s="2"/>
@@ -18374,52 +18378,52 @@
     </row>
     <row r="35" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="str">
-        <f>Thermonix!A34</f>
-        <v>Transition</v>
+        <f>Thermonix!A35</f>
+        <v>Guard</v>
       </c>
       <c r="B35" s="4" t="str">
-        <f>Thermonix!B34</f>
-        <v>next (Chop ⇒ Cook)</v>
+        <f>Thermonix!B35</f>
+        <v>[choppingTimeDone &amp;&amp; !moreIngredientsRequired()]</v>
       </c>
       <c r="C35" s="25">
-        <f>'Thermonix Grader #1'!C34</f>
-        <v>1</v>
+        <f>'Thermonix Grader #1'!C35</f>
+        <v>0</v>
       </c>
       <c r="D35" s="25">
-        <f>'Thermonix Grader #2'!C34</f>
-        <v>1</v>
+        <f>'Thermonix Grader #2'!C35</f>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="str">
-        <f>Thermonix!A35</f>
-        <v>Guard</v>
+        <f>Thermonix!A36</f>
+        <v>Action</v>
       </c>
       <c r="B36" s="4" t="str">
-        <f>Thermonix!B35</f>
-        <v>[choppingTimeDone &amp;&amp; !moreIngredientsRequired()]</v>
+        <f>Thermonix!B36</f>
+        <v>setCookingSpeedAndTime()</v>
       </c>
       <c r="C36" s="25">
-        <f>'Thermonix Grader #1'!C35</f>
-        <v>0</v>
+        <f>'Thermonix Grader #1'!C36</f>
+        <v>1</v>
       </c>
       <c r="D36" s="25">
-        <f>'Thermonix Grader #2'!C35</f>
+        <f>'Thermonix Grader #2'!C36</f>
         <v>0</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="79" t="s">
+      <c r="F36" s="76" t="s">
         <v>104</v>
       </c>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="80"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="81" t="s">
+      <c r="L36" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="M36" s="82"/>
-      <c r="N36" s="82"/>
+      <c r="M36" s="81"/>
+      <c r="N36" s="81"/>
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
@@ -18429,20 +18433,20 @@
     </row>
     <row r="37" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="str">
-        <f>Thermonix!A36</f>
-        <v>Action</v>
+        <f>Thermonix!A37</f>
+        <v>State</v>
       </c>
       <c r="B37" s="4" t="str">
-        <f>Thermonix!B36</f>
-        <v>setCookingSpeedAndTime()</v>
+        <f>Thermonix!B37</f>
+        <v>Cook</v>
       </c>
       <c r="C37" s="25">
-        <f>'Thermonix Grader #1'!C36</f>
+        <f>'Thermonix Grader #1'!C37</f>
         <v>1</v>
       </c>
       <c r="D37" s="25">
-        <f>'Thermonix Grader #2'!C36</f>
-        <v>0</v>
+        <f>'Thermonix Grader #2'!C37</f>
+        <v>1</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="2" t="s">
@@ -18479,39 +18483,39 @@
     </row>
     <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="str">
-        <f>Thermonix!A37</f>
-        <v>State</v>
+        <f>Thermonix!A38</f>
+        <v>Transition</v>
       </c>
       <c r="B38" s="4" t="str">
-        <f>Thermonix!B37</f>
-        <v>Cook</v>
+        <f>Thermonix!B38</f>
+        <v>after choppingTime (Cook ⇒ PromptToAdd)</v>
       </c>
       <c r="C38" s="25">
-        <f>'Thermonix Grader #1'!C37</f>
-        <v>1</v>
+        <f>'Thermonix Grader #1'!C38</f>
+        <v>0</v>
       </c>
       <c r="D38" s="25">
-        <f>'Thermonix Grader #2'!C37</f>
-        <v>1</v>
+        <f>'Thermonix Grader #2'!C38</f>
+        <v>0</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="44">
         <v>0</v>
       </c>
       <c r="G38" s="45">
-        <f t="shared" ref="G38:H38" si="21">COUNTIFS($A$2:$A$89,$F$37,$C$2:$C$89,$F38,$D$2:$D$89,G$37)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F38,$D$2:$D$88,G$37)</f>
         <v>5</v>
       </c>
       <c r="H38" s="46">
-        <f t="shared" si="21"/>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F38,$D$2:$D$88,H$37)</f>
         <v>0</v>
       </c>
       <c r="I38" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$37,$C$2:$C$45,$F38,$D$2:$D$45,I$37)+MAX(D49-C49,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$37,$C$2:$C$44,$F38,$D$2:$D$44,I$37)+MAX(D48-C48,0)</f>
         <v>0</v>
       </c>
       <c r="J38" s="2">
-        <f t="shared" ref="J38:J40" si="22">SUM(G38:I38)</f>
+        <f t="shared" ref="J38:J40" si="10">SUM(G38:I38)</f>
         <v>5</v>
       </c>
       <c r="K38" s="2"/>
@@ -18519,7 +18523,7 @@
         <v>90</v>
       </c>
       <c r="M38" s="45">
-        <f>(G38+H39+I40)/COUNTIF($A$2:$A$99,F37)</f>
+        <f>(G38+H39+I40)/COUNTIF($A$2:$A$98,F37)</f>
         <v>0.7142857142857143</v>
       </c>
       <c r="N38" s="47" t="s">
@@ -18534,19 +18538,19 @@
     </row>
     <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="str">
-        <f>Thermonix!A38</f>
-        <v>Transition</v>
+        <f>Thermonix!A39</f>
+        <v>Guard</v>
       </c>
       <c r="B39" s="4" t="str">
-        <f>Thermonix!B38</f>
-        <v>after choppingTime (Cook ⇒ PromptToAdd)</v>
+        <f>Thermonix!B39</f>
+        <v>[choppingTimeDone &amp;&amp; moreIngredientsRequired()]</v>
       </c>
       <c r="C39" s="25">
-        <f>'Thermonix Grader #1'!C38</f>
+        <f>'Thermonix Grader #1'!C39</f>
         <v>0</v>
       </c>
       <c r="D39" s="25">
-        <f>'Thermonix Grader #2'!C38</f>
+        <f>'Thermonix Grader #2'!C39</f>
         <v>0</v>
       </c>
       <c r="E39" s="5"/>
@@ -18554,19 +18558,19 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="49">
-        <f t="shared" ref="G39:I39" si="23">COUNTIFS($A$2:$A$89,$F$37,$C$2:$C$89,$F39,$D$2:$D$89,G$37)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F39,$D$2:$D$88,G$37)</f>
         <v>0</v>
       </c>
       <c r="H39" s="2">
-        <f t="shared" si="23"/>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F39,$D$2:$D$88,H$37)</f>
         <v>0</v>
       </c>
       <c r="I39" s="50">
-        <f t="shared" si="23"/>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F39,$D$2:$D$88,I$37)</f>
         <v>0</v>
       </c>
       <c r="J39" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K39" s="2"/>
@@ -18574,7 +18578,7 @@
         <v>92</v>
       </c>
       <c r="M39" s="49">
-        <f t="array" ref="M39">SUMPRODUCT(J38:J40/COUNTIF($A$2:$A$99,F37), TRANSPOSE(G41:I41)/COUNTIF($A$2:$A$99,F37))</f>
+        <f t="array" ref="M39">SUMPRODUCT(J38:J40/COUNTIF($A$2:$A$98,F37), TRANSPOSE(G41:I41)/COUNTIF($A$2:$A$98,F37))</f>
         <v>0.7142857142857143</v>
       </c>
       <c r="N39" s="50" t="s">
@@ -18589,19 +18593,19 @@
     </row>
     <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="str">
-        <f>Thermonix!A39</f>
-        <v>Guard</v>
+        <f>Thermonix!A40</f>
+        <v>Action</v>
       </c>
       <c r="B40" s="4" t="str">
-        <f>Thermonix!B39</f>
-        <v>[choppingTimeDone &amp;&amp; moreIngredientsRequired()]</v>
+        <f>Thermonix!B40</f>
+        <v>setIngredients()</v>
       </c>
       <c r="C40" s="25">
-        <f>'Thermonix Grader #1'!C39</f>
+        <f>'Thermonix Grader #1'!C40</f>
         <v>0</v>
       </c>
       <c r="D40" s="25">
-        <f>'Thermonix Grader #2'!C39</f>
+        <f>'Thermonix Grader #2'!C40</f>
         <v>0</v>
       </c>
       <c r="E40" s="5"/>
@@ -18609,19 +18613,19 @@
         <v>1</v>
       </c>
       <c r="G40" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$37,$C$2:$C$45,$F40,$D$2:$D$45,G$37)+MAX(C49-D49,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$37,$C$2:$C$44,$F40,$D$2:$D$44,G$37)+MAX(C48-D48,0)</f>
         <v>2</v>
       </c>
       <c r="H40" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$37,$C$2:$C$89,$F40,$D$2:$D$89,H$37)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F40,$D$2:$D$88,H$37)</f>
         <v>0</v>
       </c>
       <c r="I40" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$37,$C$2:$C$45,$F40,$D$2:$D$45,I$37) + MIN(C49,D49)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$37,$C$2:$C$44,$F40,$D$2:$D$44,I$37) + MIN(C48,D48)</f>
         <v>0</v>
       </c>
       <c r="J40" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="L40" s="48" t="s">
@@ -18643,35 +18647,35 @@
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="str">
-        <f>Thermonix!A40</f>
-        <v>Action</v>
+        <f>Thermonix!A41</f>
+        <v>Transition</v>
       </c>
       <c r="B41" s="4" t="str">
-        <f>Thermonix!B40</f>
-        <v>setIngredients()</v>
+        <f>Thermonix!B41</f>
+        <v>after cookingTime (Cook ⇒ Ready)</v>
       </c>
       <c r="C41" s="25">
-        <f>'Thermonix Grader #1'!C40</f>
-        <v>0</v>
+        <f>'Thermonix Grader #1'!C41</f>
+        <v>1</v>
       </c>
       <c r="D41" s="25">
-        <f>'Thermonix Grader #2'!C40</f>
-        <v>0</v>
+        <f>'Thermonix Grader #2'!C41</f>
+        <v>1</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="54" t="s">
         <v>95</v>
       </c>
       <c r="G41" s="2">
-        <f t="shared" ref="G41:I41" si="24">SUM(G38:G40)</f>
+        <f t="shared" ref="G41:I41" si="11">SUM(G38:G40)</f>
         <v>7</v>
       </c>
       <c r="H41" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I41" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J41" s="2"/>
@@ -18686,20 +18690,20 @@
     </row>
     <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="str">
-        <f>Thermonix!A41</f>
-        <v>Transition</v>
+        <f>Thermonix!A42</f>
+        <v>Guard</v>
       </c>
       <c r="B42" s="4" t="str">
-        <f>Thermonix!B41</f>
-        <v>after cookingTime (Cook ⇒ Ready)</v>
+        <f>Thermonix!B42</f>
+        <v>[!moreIngredientsRequired()]</v>
       </c>
       <c r="C42" s="25">
-        <f>'Thermonix Grader #1'!C41</f>
+        <f>'Thermonix Grader #1'!C42</f>
         <v>1</v>
       </c>
       <c r="D42" s="25">
-        <f>'Thermonix Grader #2'!C41</f>
-        <v>1</v>
+        <f>'Thermonix Grader #2'!C42</f>
+        <v>0.5</v>
       </c>
       <c r="E42" s="5"/>
       <c r="O42" s="5"/>
@@ -18711,34 +18715,34 @@
     </row>
     <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="str">
-        <f>Thermonix!A42</f>
-        <v>Guard</v>
+        <f>Thermonix!A43</f>
+        <v>State</v>
       </c>
       <c r="B43" s="4" t="str">
-        <f>Thermonix!B42</f>
-        <v>[!moreIngredientsRequired()]</v>
+        <f>Thermonix!B43</f>
+        <v>Ready</v>
       </c>
       <c r="C43" s="25">
-        <f>'Thermonix Grader #1'!C42</f>
+        <f>'Thermonix Grader #1'!C43</f>
         <v>1</v>
       </c>
       <c r="D43" s="25">
-        <f>'Thermonix Grader #2'!C42</f>
-        <v>0.5</v>
+        <f>'Thermonix Grader #2'!C43</f>
+        <v>1</v>
       </c>
       <c r="E43" s="5"/>
-      <c r="F43" s="79" t="s">
+      <c r="F43" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="G43" s="80"/>
-      <c r="H43" s="80"/>
-      <c r="I43" s="80"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
+      <c r="I43" s="77"/>
       <c r="K43" s="2"/>
-      <c r="L43" s="81" t="s">
+      <c r="L43" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="M43" s="82"/>
-      <c r="N43" s="82"/>
+      <c r="M43" s="81"/>
+      <c r="N43" s="81"/>
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
       <c r="Q43" s="5"/>
@@ -18747,20 +18751,20 @@
       <c r="T43" s="5"/>
     </row>
     <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="3" t="str">
-        <f>Thermonix!A43</f>
-        <v>State</v>
-      </c>
-      <c r="B44" s="4" t="str">
-        <f>Thermonix!B43</f>
-        <v>Ready</v>
-      </c>
-      <c r="C44" s="25">
-        <f>'Thermonix Grader #1'!C43</f>
-        <v>1</v>
-      </c>
-      <c r="D44" s="25">
-        <f>'Thermonix Grader #2'!C43</f>
+      <c r="A44" s="73" t="str">
+        <f>Thermonix!A44</f>
+        <v>Transition</v>
+      </c>
+      <c r="B44" s="74" t="str">
+        <f>Thermonix!B44</f>
+        <v>after 14min 30sec (Ready ⇒ Preparing Shutdown)</v>
+      </c>
+      <c r="C44" s="75">
+        <f>'Thermonix Grader #1'!C44</f>
+        <v>1</v>
+      </c>
+      <c r="D44" s="75">
+        <f>'Thermonix Grader #2'!C44</f>
         <v>1</v>
       </c>
       <c r="E44" s="5"/>
@@ -18798,39 +18802,39 @@
     </row>
     <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="str">
-        <f>Thermonix!A44</f>
-        <v>Transition</v>
+        <f>Thermonix!A45</f>
+        <v>State</v>
       </c>
       <c r="B45" s="4" t="str">
-        <f>Thermonix!B44</f>
-        <v>after 14min 30sec (Ready ⇒ Preparing Shutdown)</v>
-      </c>
-      <c r="C45" s="59">
-        <f>'Thermonix Grader #1'!C44</f>
-        <v>1</v>
-      </c>
-      <c r="D45" s="59">
-        <f>'Thermonix Grader #2'!C44</f>
-        <v>1</v>
+        <f>Thermonix!B45</f>
+        <v>additional elements</v>
+      </c>
+      <c r="C45" s="25">
+        <f>'Thermonix Grader #1'!C45</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="25">
+        <f>'Thermonix Grader #2'!C45</f>
+        <v>0</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="44">
         <v>0</v>
       </c>
       <c r="G45" s="45">
-        <f t="shared" ref="G45:H45" si="25">COUNTIFS($A$2:$A$89,$F$44,$C$2:$C$89,$F45,$D$2:$D$89,G$44)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F45,$D$2:$D$88,G$44)</f>
         <v>2</v>
       </c>
       <c r="H45" s="46">
-        <f t="shared" si="25"/>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F45,$D$2:$D$88,H$44)</f>
         <v>0</v>
       </c>
       <c r="I45" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$44,$C$2:$C$45,$F45,$D$2:$D$45,I$44) + MAX(D52-C52,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$44,$C$2:$C$44,$F45,$D$2:$D$44,I$44) + MAX(D51-C51,0)</f>
         <v>0</v>
       </c>
       <c r="J45" s="2">
-        <f t="shared" ref="J45:J47" si="26">SUM(G45:I45)</f>
+        <f t="shared" ref="J45:J47" si="12">SUM(G45:I45)</f>
         <v>2</v>
       </c>
       <c r="K45" s="2"/>
@@ -18838,7 +18842,7 @@
         <v>90</v>
       </c>
       <c r="M45" s="45">
-        <f>(G45+H46+I47)/COUNTIF($A$2:$A$99,F44)</f>
+        <f>(G45+H46+I47)/COUNTIF($A$2:$A$98,F44)</f>
         <v>1</v>
       </c>
       <c r="N45" s="47" t="s">
@@ -18852,39 +18856,39 @@
       <c r="T45" s="5"/>
     </row>
     <row r="46" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="60" t="str">
-        <f>Thermonix!A45</f>
-        <v>State</v>
-      </c>
-      <c r="B46" s="61" t="str">
-        <f>Thermonix!B45</f>
+      <c r="A46" s="3" t="str">
+        <f>Thermonix!A46</f>
+        <v>Transition</v>
+      </c>
+      <c r="B46" s="4" t="str">
+        <f>Thermonix!B46</f>
         <v>additional elements</v>
       </c>
-      <c r="C46" s="62">
-        <f>'Thermonix Grader #1'!C45</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="62">
-        <f>'Thermonix Grader #2'!C45</f>
+      <c r="C46" s="25">
+        <f>'Thermonix Grader #1'!C46</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="25">
+        <f>'Thermonix Grader #2'!C46</f>
         <v>0</v>
       </c>
       <c r="F46" s="44">
         <v>0.5</v>
       </c>
       <c r="G46" s="49">
-        <f t="shared" ref="G46:I46" si="27">COUNTIFS($A$2:$A$89,$F$44,$C$2:$C$89,$F46,$D$2:$D$89,G$44)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F46,$D$2:$D$88,G$44)</f>
         <v>0</v>
       </c>
       <c r="H46" s="2">
-        <f t="shared" si="27"/>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F46,$D$2:$D$88,H$44)</f>
         <v>0</v>
       </c>
       <c r="I46" s="50">
-        <f t="shared" si="27"/>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F46,$D$2:$D$88,I$44)</f>
         <v>0</v>
       </c>
       <c r="J46" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K46" s="2"/>
@@ -18892,7 +18896,7 @@
         <v>92</v>
       </c>
       <c r="M46" s="49">
-        <f t="array" ref="M46">SUMPRODUCT(J45:J47/COUNTIF($A$2:$A$99,F44), TRANSPOSE(G48:I48)/COUNTIF($A$2:$A$99,F44))</f>
+        <f t="array" ref="M46">SUMPRODUCT(J45:J47/COUNTIF($A$2:$A$98,F44), TRANSPOSE(G48:I48)/COUNTIF($A$2:$A$98,F44))</f>
         <v>1</v>
       </c>
       <c r="N46" s="50" t="s">
@@ -18901,38 +18905,38 @@
     </row>
     <row r="47" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="str">
-        <f>Thermonix!A46</f>
-        <v>Transition</v>
+        <f>Thermonix!A47</f>
+        <v>Guard</v>
       </c>
       <c r="B47" s="4" t="str">
-        <f>Thermonix!B46</f>
+        <f>Thermonix!B47</f>
         <v>additional elements</v>
       </c>
       <c r="C47" s="25">
-        <f>'Thermonix Grader #1'!C46</f>
+        <f>'Thermonix Grader #1'!C47</f>
         <v>0</v>
       </c>
       <c r="D47" s="25">
-        <f>'Thermonix Grader #2'!C46</f>
+        <f>'Thermonix Grader #2'!C47</f>
         <v>0</v>
       </c>
       <c r="F47" s="44">
         <v>1</v>
       </c>
       <c r="G47" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$44,$C$2:$C$45,$F47,$D$2:$D$45,G$44) + MAX(C52-D52,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$44,$C$2:$C$44,$F47,$D$2:$D$44,G$44) + MAX(C51-D51,0)</f>
         <v>0</v>
       </c>
       <c r="H47" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$44,$C$2:$C$89,$F47,$D$2:$D$89,H$44)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F47,$D$2:$D$88,H$44)</f>
         <v>0</v>
       </c>
       <c r="I47" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$44,$C$2:$C$45,$F47,$D$2:$D$45,I$44) + MIN(C52,D52)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$44,$C$2:$C$44,$F47,$D$2:$D$44,I$44) + MIN(C51,D51)</f>
         <v>0</v>
       </c>
       <c r="J47" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L47" s="48" t="s">
@@ -18948,34 +18952,34 @@
     </row>
     <row r="48" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="str">
-        <f>Thermonix!A47</f>
-        <v>Guard</v>
+        <f>Thermonix!A48</f>
+        <v>Action</v>
       </c>
       <c r="B48" s="4" t="str">
-        <f>Thermonix!B47</f>
+        <f>Thermonix!B48</f>
         <v>additional elements</v>
       </c>
       <c r="C48" s="25">
-        <f>'Thermonix Grader #1'!C47</f>
+        <f>'Thermonix Grader #1'!C48</f>
         <v>0</v>
       </c>
       <c r="D48" s="25">
-        <f>'Thermonix Grader #2'!C47</f>
+        <f>'Thermonix Grader #2'!C48</f>
         <v>0</v>
       </c>
       <c r="F48" s="54" t="s">
         <v>95</v>
       </c>
       <c r="G48" s="2">
-        <f t="shared" ref="G48:I48" si="28">SUM(G45:G47)</f>
+        <f t="shared" ref="G48:I48" si="13">SUM(G45:G47)</f>
         <v>2</v>
       </c>
       <c r="H48" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I48" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J48" s="2"/>
@@ -18984,67 +18988,67 @@
     </row>
     <row r="49" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="3" t="str">
-        <f>Thermonix!A48</f>
-        <v>Action</v>
+        <f>Thermonix!A49</f>
+        <v>Composite State</v>
       </c>
       <c r="B49" s="4" t="str">
-        <f>Thermonix!B48</f>
+        <f>Thermonix!B49</f>
         <v>additional elements</v>
       </c>
       <c r="C49" s="25">
-        <f>'Thermonix Grader #1'!C48</f>
+        <f>'Thermonix Grader #1'!C49</f>
         <v>0</v>
       </c>
       <c r="D49" s="25">
-        <f>'Thermonix Grader #2'!C48</f>
+        <f>'Thermonix Grader #2'!C49</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="str">
-        <f>Thermonix!A49</f>
-        <v>Composite State</v>
+        <f>Thermonix!A50</f>
+        <v>Region</v>
       </c>
       <c r="B50" s="4" t="str">
-        <f>Thermonix!B49</f>
+        <f>Thermonix!B50</f>
         <v>additional elements</v>
       </c>
       <c r="C50" s="25">
-        <f>'Thermonix Grader #1'!C49</f>
+        <f>'Thermonix Grader #1'!C50</f>
         <v>0</v>
       </c>
       <c r="D50" s="25">
-        <f>'Thermonix Grader #2'!C49</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="79" t="s">
+        <f>'Thermonix Grader #2'!C50</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="76" t="s">
         <v>108</v>
       </c>
-      <c r="G50" s="80"/>
-      <c r="H50" s="80"/>
-      <c r="I50" s="80"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="77"/>
+      <c r="I50" s="77"/>
       <c r="K50" s="2"/>
-      <c r="L50" s="81" t="s">
+      <c r="L50" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="M50" s="82"/>
-      <c r="N50" s="82"/>
+      <c r="M50" s="81"/>
+      <c r="N50" s="81"/>
     </row>
     <row r="51" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="str">
-        <f>Thermonix!A50</f>
-        <v>Region</v>
+        <f>Thermonix!A51</f>
+        <v>History State</v>
       </c>
       <c r="B51" s="4" t="str">
-        <f>Thermonix!B50</f>
+        <f>Thermonix!B51</f>
         <v>additional elements</v>
       </c>
       <c r="C51" s="25">
-        <f>'Thermonix Grader #1'!C50</f>
+        <f>'Thermonix Grader #1'!C51</f>
         <v>0</v>
       </c>
       <c r="D51" s="25">
-        <f>'Thermonix Grader #2'!C50</f>
+        <f>'Thermonix Grader #2'!C51</f>
         <v>0</v>
       </c>
       <c r="F51" s="2" t="s">
@@ -19074,39 +19078,27 @@
       </c>
     </row>
     <row r="52" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="3" t="str">
-        <f>Thermonix!A51</f>
-        <v>History State</v>
-      </c>
-      <c r="B52" s="4" t="str">
-        <f>Thermonix!B51</f>
-        <v>additional elements</v>
-      </c>
-      <c r="C52" s="25">
-        <f>'Thermonix Grader #1'!C51</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="25">
-        <f>'Thermonix Grader #2'!C51</f>
-        <v>0</v>
-      </c>
+      <c r="A52" s="3"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
       <c r="F52" s="44">
         <v>0</v>
       </c>
       <c r="G52" s="45">
-        <f t="shared" ref="G52:H52" si="29">COUNTIFS($A$2:$A$89,$F$51,$C$2:$C$89,$F52,$D$2:$D$89,G$51)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F52,$D$2:$D$88,G$51)</f>
         <v>1</v>
       </c>
       <c r="H52" s="46">
-        <f t="shared" si="29"/>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F52,$D$2:$D$88,H$51)</f>
         <v>0</v>
       </c>
       <c r="I52" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$51,$C$2:$C$45,$F52,$D$2:$D$45,I$51)+MAX(D51-C51,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$51,$C$2:$C$44,$F52,$D$2:$D$44,I$51)+MAX(D50-C50,0)</f>
         <v>0</v>
       </c>
       <c r="J52" s="2">
-        <f t="shared" ref="J52:J54" si="30">SUM(G52:I52)</f>
+        <f t="shared" ref="J52:J54" si="14">SUM(G52:I52)</f>
         <v>1</v>
       </c>
       <c r="K52" s="2"/>
@@ -19114,7 +19106,7 @@
         <v>90</v>
       </c>
       <c r="M52" s="45">
-        <f>(G52+H53+I54)/COUNTIF($A$2:$A$99,F51)</f>
+        <f>(G52+H53+I54)/COUNTIF($A$2:$A$98,F51)</f>
         <v>1</v>
       </c>
       <c r="N52" s="47" t="s">
@@ -19130,19 +19122,19 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="49">
-        <f t="shared" ref="G53:I53" si="31">COUNTIFS($A$2:$A$89,$F$51,$C$2:$C$89,$F53,$D$2:$D$89,G$51)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F53,$D$2:$D$88,G$51)</f>
         <v>0</v>
       </c>
       <c r="H53" s="2">
-        <f t="shared" si="31"/>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F53,$D$2:$D$88,H$51)</f>
         <v>0</v>
       </c>
       <c r="I53" s="50">
-        <f t="shared" si="31"/>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F53,$D$2:$D$88,I$51)</f>
         <v>0</v>
       </c>
       <c r="J53" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K53" s="2"/>
@@ -19150,7 +19142,7 @@
         <v>92</v>
       </c>
       <c r="M53" s="49">
-        <f t="array" ref="M53">SUMPRODUCT(J52:J54/COUNTIF($A$2:$A$99,F51), TRANSPOSE(G55:I55)/COUNTIF($A$2:$A$99,F51))</f>
+        <f t="array" ref="M53">SUMPRODUCT(J52:J54/COUNTIF($A$2:$A$98,F51), TRANSPOSE(G55:I55)/COUNTIF($A$2:$A$98,F51))</f>
         <v>1</v>
       </c>
       <c r="N53" s="50" t="s">
@@ -19166,19 +19158,19 @@
         <v>1</v>
       </c>
       <c r="G54" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$51,$C$2:$C$45,$F54,$D$2:$D$45,G$51) + MAX(C51-D51,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$51,$C$2:$C$44,$F54,$D$2:$D$44,G$51) + MAX(C50-D50,0)</f>
         <v>0</v>
       </c>
       <c r="H54" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$51,$C$2:$C$89,$F54,$D$2:$D$89,H$51)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F54,$D$2:$D$88,H$51)</f>
         <v>0</v>
       </c>
       <c r="I54" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$51,$C$2:$C$45,$F54,$D$2:$D$45,I$51)+MIN(C51,D51)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$51,$C$2:$C$44,$F54,$D$2:$D$44,I$51)+MIN(C50,D50)</f>
         <v>0</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L54" s="48" t="s">
@@ -19201,15 +19193,15 @@
         <v>95</v>
       </c>
       <c r="G55" s="2">
-        <f t="shared" ref="G55:I55" si="32">SUM(G52:G54)</f>
+        <f t="shared" ref="G55:I55" si="15">SUM(G52:G54)</f>
         <v>1</v>
       </c>
       <c r="H55" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I55" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J55" s="2"/>
@@ -19333,7 +19325,6 @@
     <row r="75" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3"/>
       <c r="B75" s="4"/>
-      <c r="C75" s="5"/>
       <c r="D75" s="5"/>
     </row>
     <row r="76" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19379,11 +19370,10 @@
     <row r="84" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="3"/>
       <c r="B84" s="4"/>
-      <c r="D84" s="5"/>
     </row>
     <row r="85" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="3"/>
-      <c r="B85" s="4"/>
+      <c r="A85" s="1"/>
+      <c r="B85" s="2"/>
     </row>
     <row r="86" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="1"/>
@@ -20121,10 +20111,7 @@
       <c r="A269" s="1"/>
       <c r="B269" s="2"/>
     </row>
-    <row r="270" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A270" s="1"/>
-      <c r="B270" s="2"/>
-    </row>
+    <row r="270" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="271" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="272" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -20917,18 +20904,18 @@
       <c r="D1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="L1" s="79" t="s">
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="L1" s="76" t="s">
         <v>110</v>
       </c>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
     </row>
     <row r="2" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="str">
@@ -21020,15 +21007,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="45">
-        <f>COUNTIFS($C$2:$C$89, $F3, $D$2:$D$89, G$2)</f>
+        <f>COUNTIFS($C$2:$C$88, $F3, $D$2:$D$88, G$2)</f>
         <v>22</v>
       </c>
       <c r="H3" s="46">
-        <f>COUNTIFS($C$2:$C$45, $F3, $D$2:$D$45, H$2)</f>
+        <f>COUNTIFS($C$2:$C$44, $F3, $D$2:$D$44, H$2)</f>
         <v>0</v>
       </c>
       <c r="I3" s="47">
-        <f>COUNTIFS($C$2:$C$45, $F3, $D$2:$D$45, I$2)+MAX(D46-C46,0)+MAX(D47-C47,0)+MAX(D48-C48,0)+MAX(D49-C49,0)+MAX(D50-C50,0)+MAX(D51-C51,0)+MAX(D52-C52,0)</f>
+        <f>COUNTIFS($C$2:$C$44, $F3, $D$2:$D$44, I$2)+MAX(D45-C45,0)+MAX(D46-C46,0)+MAX(D47-C47,0)+MAX(D48-C48,0)+MAX(D49-C49,0)+MAX(D50-C50,0)+MAX(D51-C51,0)</f>
         <v>5</v>
       </c>
       <c r="J3" s="2">
@@ -21057,15 +21044,15 @@
       </c>
       <c r="R3" s="45">
         <f t="shared" ref="R3:T3" si="2">($J3/$J$6) * (G$6/$J$6)</f>
-        <v>0.26988754685547683</v>
+        <v>0.27</v>
       </c>
       <c r="S3" s="46">
         <f t="shared" si="2"/>
-        <v>1.1245314452311535E-2</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="T3" s="47">
         <f t="shared" si="2"/>
-        <v>0.26988754685547683</v>
+        <v>0.25919999999999999</v>
       </c>
       <c r="U3" s="2"/>
       <c r="V3" s="48" t="s">
@@ -21073,7 +21060,7 @@
       </c>
       <c r="W3" s="45">
         <f>SUMPRODUCT(G3:I5, M3:O5) /$J$6</f>
-        <v>0.15306122448979592</v>
+        <v>0.16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>112</v>
@@ -21100,27 +21087,27 @@
         <v>0.5</v>
       </c>
       <c r="G4" s="49">
-        <f t="shared" ref="G4:I4" si="3">COUNTIFS($C$2:$C$45, $F4, $D$2:$D$45, G$2)</f>
-        <v>0</v>
+        <f>COUNTIFS($C$2:$C$44, $F4, $D$2:$D$44, G$2)</f>
+        <v>1</v>
       </c>
       <c r="H4" s="2">
-        <f t="shared" si="3"/>
+        <f>COUNTIFS($C$2:$C$44, $F4, $D$2:$D$44, H$2)</f>
         <v>0</v>
       </c>
       <c r="I4" s="50">
-        <f t="shared" si="3"/>
+        <f>COUNTIFS($C$2:$C$44, $F4, $D$2:$D$44, I$2)</f>
         <v>0</v>
       </c>
       <c r="J4" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="44">
         <v>0.5</v>
       </c>
       <c r="M4" s="49">
-        <f t="shared" ref="M4:M5" si="4">ABS(G$2-$F4)/1</f>
+        <f t="shared" ref="M4:M5" si="3">ABS(G$2-$F4)/1</f>
         <v>0.5</v>
       </c>
       <c r="N4" s="2">
@@ -21136,16 +21123,16 @@
         <v>0.5</v>
       </c>
       <c r="R4" s="49">
-        <f t="shared" ref="R4:T4" si="5">($J4/$J$6) * (G$6/$J$6)</f>
-        <v>0</v>
+        <f t="shared" ref="R4:T4" si="4">($J4/$J$6) * (G$6/$J$6)</f>
+        <v>0.01</v>
       </c>
       <c r="S4" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="T4" s="50">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="U4" s="2"/>
       <c r="V4" s="48" t="s">
@@ -21153,7 +21140,7 @@
       </c>
       <c r="W4" s="49">
         <f>SUMPRODUCT(R3:T5, M3:O5)</f>
-        <v>0.49999999999999994</v>
+        <v>0.49880000000000008</v>
       </c>
       <c r="X4" s="50" t="s">
         <v>114</v>
@@ -21180,15 +21167,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="51">
-        <f>COUNTIFS($C$2:$C$45, $F5, $D$2:$D$45, G$2)+MAX(C46-D46,0)+MAX(C47-D47,0)+MAX(C48-D48,0)+MAX(C49-D49,0)+MAX(C50-D50,0)+MAX(C51-D51,0)+MAX(C52-D52,0)</f>
+        <f>COUNTIFS($C$2:$C$44, $F5, $D$2:$D$44, G$2)+MAX(C45-D45,0)+MAX(C46-D46,0)+MAX(C47-D47,0)+MAX(C48-D48,0)+MAX(C49-D49,0)+MAX(C50-D50,0)+MAX(C51-D51,0)</f>
         <v>2</v>
       </c>
       <c r="H5" s="52">
-        <f>COUNTIFS($C$2:$C$45, $F5, $D$2:$D$45, H$2)</f>
+        <f>COUNTIFS($C$2:$C$44, $F5, $D$2:$D$44, H$2)</f>
         <v>1</v>
       </c>
       <c r="I5" s="53">
-        <f>COUNTIFS($C$2:$C$45, $F5, $D$2:$D$45, I$2)+ SUM(MIN(C46,D46), MIN(C47,D47), MIN(C48,D48), MIN(C49,D49), MIN(C50,D50), MIN(C51,D51), MIN(C52,D52))</f>
+        <f>COUNTIFS($C$2:$C$44, $F5, $D$2:$D$44, I$2)+ SUM(MIN(C45,D45), MIN(C46,D46), MIN(C47,D47), MIN(C48,D48), MIN(C49,D49), MIN(C50,D50), MIN(C51,D51))</f>
         <v>19</v>
       </c>
       <c r="J5" s="2">
@@ -21200,15 +21187,15 @@
         <v>1</v>
       </c>
       <c r="M5" s="51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N5" s="52">
-        <f t="shared" ref="N5:O5" si="6">ABS(H$2-$F5)/1</f>
+        <f t="shared" ref="N5:O5" si="5">ABS(H$2-$F5)/1</f>
         <v>0.5</v>
       </c>
       <c r="O5" s="53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P5" s="2"/>
@@ -21216,16 +21203,16 @@
         <v>1</v>
       </c>
       <c r="R5" s="51">
-        <f t="shared" ref="R5:T5" si="7">($J5/$J$6) * (G$6/$J$6)</f>
-        <v>0.21990837151187004</v>
+        <f t="shared" ref="R5:T5" si="6">($J5/$J$6) * (G$6/$J$6)</f>
+        <v>0.22</v>
       </c>
       <c r="S5" s="52">
-        <f t="shared" si="7"/>
-        <v>9.1628488129945843E-3</v>
+        <f t="shared" si="6"/>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="T5" s="53">
-        <f t="shared" si="7"/>
-        <v>0.21990837151187004</v>
+        <f t="shared" si="6"/>
+        <v>0.2112</v>
       </c>
       <c r="U5" s="2"/>
       <c r="V5" s="48" t="s">
@@ -21233,7 +21220,7 @@
       </c>
       <c r="W5" s="51">
         <f>1-W3/W4</f>
-        <v>0.69387755102040805</v>
+        <v>0.67923015236567763</v>
       </c>
       <c r="X5" s="53" t="s">
         <v>115</v>
@@ -21260,20 +21247,20 @@
         <v>95</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" ref="G6:I6" si="8">SUM(G3:G5)</f>
-        <v>24</v>
+        <f t="shared" ref="G6:I6" si="7">SUM(G3:G5)</f>
+        <v>25</v>
       </c>
       <c r="H6" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I6" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="J6" s="2">
         <f>SUM(G3:I5)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -21325,12 +21312,12 @@
         <f>'Thermonix Grader #2'!C8</f>
         <v>1</v>
       </c>
-      <c r="F8" s="79" t="s">
+      <c r="F8" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="str">
@@ -21352,13 +21339,13 @@
       <c r="F9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="63" t="s">
+      <c r="G9" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="H9" s="63" t="s">
+      <c r="H9" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="I9" s="63" t="s">
+      <c r="I9" s="59" t="s">
         <v>85</v>
       </c>
       <c r="J9" s="57" t="s">
@@ -21368,36 +21355,36 @@
       <c r="L9" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M9" s="63" t="s">
+      <c r="M9" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="N9" s="63" t="s">
+      <c r="N9" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="O9" s="63" t="s">
+      <c r="O9" s="59" t="s">
         <v>85</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="R9" s="63" t="s">
+      <c r="R9" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="S9" s="63" t="s">
+      <c r="S9" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="T9" s="63" t="s">
+      <c r="T9" s="59" t="s">
         <v>85</v>
       </c>
       <c r="V9" s="43" t="str">
         <f>"Metrics" &amp; " " &amp; F9</f>
         <v>Metrics State</v>
       </c>
-      <c r="W9" s="64" t="s">
+      <c r="W9" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="X9" s="64" t="s">
+      <c r="X9" s="60" t="s">
         <v>89</v>
       </c>
     </row>
@@ -21418,55 +21405,55 @@
         <f>'Thermonix Grader #2'!C10</f>
         <v>1</v>
       </c>
-      <c r="F10" s="65">
+      <c r="F10" s="61">
         <v>0</v>
       </c>
       <c r="G10" s="45">
-        <f t="shared" ref="G10:H10" si="9">COUNTIFS($A$2:$A$89,$F$9,$C$2:$C$89,$F10,$D$2:$D$89,G$9)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$9,$C$2:$C$88,$F10,$D$2:$D$88,G$9)</f>
         <v>3</v>
       </c>
       <c r="H10" s="46">
-        <f t="shared" si="9"/>
+        <f>COUNTIFS($A$2:$A$88,$F$9,$C$2:$C$88,$F10,$D$2:$D$88,H$9)</f>
         <v>0</v>
       </c>
       <c r="I10" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$9,$C$2:$C$45,$F10,$D$2:$D$45,I$9) + MAX(D46-C46,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$9,$C$2:$C$44,$F10,$D$2:$D$44,I$9) + MAX(D45-C45,0)</f>
         <v>1</v>
       </c>
       <c r="J10" s="2">
-        <f t="shared" ref="J10:J12" si="10">SUM(G10:I10)</f>
+        <f t="shared" ref="J10:J12" si="8">SUM(G10:I10)</f>
         <v>4</v>
       </c>
       <c r="K10" s="2"/>
-      <c r="L10" s="65">
+      <c r="L10" s="61">
         <v>0</v>
       </c>
       <c r="M10" s="45">
-        <f t="shared" ref="M10:M12" si="11">ABS(G$2-$F10)/1</f>
+        <f t="shared" ref="M10:M12" si="9">ABS(G$2-$F10)/1</f>
         <v>0</v>
       </c>
       <c r="N10" s="46">
-        <f t="shared" ref="N10:N11" si="12">ABS(H$2-$F10)/3</f>
+        <f t="shared" ref="N10:N11" si="10">ABS(H$2-$F10)/3</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="O10" s="47">
-        <f t="shared" ref="O10:O11" si="13">ABS(I$2-$F10)/1</f>
+        <f t="shared" ref="O10:O11" si="11">ABS(I$2-$F10)/1</f>
         <v>1</v>
       </c>
       <c r="P10" s="2"/>
-      <c r="Q10" s="65">
+      <c r="Q10" s="61">
         <v>0</v>
       </c>
       <c r="R10" s="45">
-        <f t="shared" ref="R10:T10" si="14">($J10/$J$13) * (G$13/$J$13)</f>
+        <f t="shared" ref="R10:T10" si="12">($J10/$J$13) * (G$13/$J$13)</f>
         <v>0</v>
       </c>
       <c r="S10" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T10" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="U10" s="2"/>
@@ -21475,7 +21462,7 @@
       </c>
       <c r="W10" s="45">
         <f>SUMPRODUCT(G3:I5, M3:O5) /$J$6</f>
-        <v>0.15306122448979592</v>
+        <v>0.16</v>
       </c>
       <c r="X10" s="47" t="s">
         <v>112</v>
@@ -21502,19 +21489,19 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="49">
-        <f t="shared" ref="G11:I11" si="15">COUNTIFS($A$2:$A$89,$F$9,$C$2:$C$89,$F11,$D$2:$D$89,G$9)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$9,$C$2:$C$88,$F11,$D$2:$D$88,G$9)</f>
         <v>0</v>
       </c>
       <c r="H11" s="2">
-        <f t="shared" si="15"/>
+        <f>COUNTIFS($A$2:$A$88,$F$9,$C$2:$C$88,$F11,$D$2:$D$88,H$9)</f>
         <v>0</v>
       </c>
       <c r="I11" s="50">
-        <f t="shared" si="15"/>
+        <f>COUNTIFS($A$2:$A$88,$F$9,$C$2:$C$88,$F11,$D$2:$D$88,I$9)</f>
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K11" s="2"/>
@@ -21522,15 +21509,15 @@
         <v>0.5</v>
       </c>
       <c r="M11" s="49">
+        <f t="shared" si="9"/>
+        <v>0.5</v>
+      </c>
+      <c r="N11" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="50">
         <f t="shared" si="11"/>
-        <v>0.5</v>
-      </c>
-      <c r="N11" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="50">
-        <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
       <c r="P11" s="2"/>
@@ -21538,15 +21525,15 @@
         <v>0.5</v>
       </c>
       <c r="R11" s="49">
-        <f t="shared" ref="R11:T11" si="16">($J11/$J$13) * (G$13/$J$13)</f>
+        <f t="shared" ref="R11:T11" si="13">($J11/$J$13) * (G$13/$J$13)</f>
         <v>0</v>
       </c>
       <c r="S11" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T11" s="50">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U11" s="2"/>
@@ -21582,19 +21569,19 @@
         <v>1</v>
       </c>
       <c r="G12" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$9,$C$2:$C$45,$F12,$D$2:$D$45,G$9)+MAX(C46-D46,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$9,$C$2:$C$44,$F12,$D$2:$D$44,G$9)+MAX(C45-D45,0)</f>
         <v>0</v>
       </c>
       <c r="H12" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$9,$C$2:$C$89,$F12,$D$2:$D$89,H$9)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$9,$C$2:$C$88,$F12,$D$2:$D$88,H$9)</f>
         <v>0</v>
       </c>
       <c r="I12" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$9,$C$2:$C$45,$F12,$D$2:$D$45,I$9)+MIN(C46-D46)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$9,$C$2:$C$44,$F12,$D$2:$D$44,I$9)+MIN(C45-D45)</f>
         <v>8</v>
       </c>
       <c r="J12" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="K12" s="2"/>
@@ -21602,15 +21589,15 @@
         <v>1</v>
       </c>
       <c r="M12" s="51">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N12" s="52">
-        <f t="shared" ref="N12:O12" si="17">ABS(H$2-$F12)/1</f>
+        <f t="shared" ref="N12:O12" si="14">ABS(H$2-$F12)/1</f>
         <v>0.5</v>
       </c>
       <c r="O12" s="53">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P12" s="2"/>
@@ -21618,15 +21605,15 @@
         <v>1</v>
       </c>
       <c r="R12" s="51">
-        <f t="shared" ref="R12:T12" si="18">($J12/$J$13) * (G$13/$J$13)</f>
+        <f t="shared" ref="R12:T12" si="15">($J12/$J$13) * (G$13/$J$13)</f>
         <v>0</v>
       </c>
       <c r="S12" s="52">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T12" s="53">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="U12" s="2"/>
@@ -21635,7 +21622,7 @@
       </c>
       <c r="W12" s="51">
         <f>1-W10/W11</f>
-        <v>0.69387755102040816</v>
+        <v>0.67999999999999994</v>
       </c>
       <c r="X12" s="53" t="s">
         <v>115</v>
@@ -21662,15 +21649,15 @@
         <v>95</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" ref="G13:I13" si="19">SUM(G11:G12)</f>
+        <f t="shared" ref="G13:I13" si="16">SUM(G11:G12)</f>
         <v>0</v>
       </c>
       <c r="H13" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>8</v>
       </c>
       <c r="J13" s="2">
@@ -21713,12 +21700,12 @@
         <f>'Thermonix Grader #2'!C15</f>
         <v>1</v>
       </c>
-      <c r="F15" s="79" t="s">
+      <c r="F15" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
     </row>
     <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="str">
@@ -21811,19 +21798,19 @@
         <v>0</v>
       </c>
       <c r="G17" s="45">
-        <f t="shared" ref="G17:H17" si="20">COUNTIFS($A$2:$A$89,$F$16,$C$2:$C$89,$F17,$D$2:$D$89,G$16)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F17,$D$2:$D$88,G$16)</f>
         <v>6</v>
       </c>
       <c r="H17" s="46">
-        <f t="shared" si="20"/>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F17,$D$2:$D$88,H$16)</f>
         <v>0</v>
       </c>
       <c r="I17" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$16,$C$2:$C$45,$F17,$D$2:$D$45,I$16) + MAX(D47-C47,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$16,$C$2:$C$44,$F17,$D$2:$D$44,I$16) + MAX(D46-C46,0)</f>
         <v>3</v>
       </c>
       <c r="J17" s="2">
-        <f t="shared" ref="J17:J19" si="21">SUM(G17:I17)</f>
+        <f t="shared" ref="J17:J19" si="17">SUM(G17:I17)</f>
         <v>9</v>
       </c>
       <c r="K17" s="2"/>
@@ -21831,15 +21818,15 @@
         <v>0</v>
       </c>
       <c r="M17" s="45">
-        <f t="shared" ref="M17:O17" si="22">ABS(G$2-$F17)/1</f>
+        <f t="shared" ref="M17:O17" si="18">ABS(G$2-$F17)/1</f>
         <v>0</v>
       </c>
       <c r="N17" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
       <c r="O17" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="P17" s="2"/>
@@ -21847,15 +21834,15 @@
         <v>0</v>
       </c>
       <c r="R17" s="45">
-        <f t="shared" ref="R17:T17" si="23">($J17/$J$20) * (G$20/$J$20)</f>
+        <f t="shared" ref="R17:T17" si="19">($J17/$J$20) * (G$20/$J$20)</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="S17" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T17" s="47">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="U17" s="2"/>
@@ -21891,19 +21878,19 @@
         <v>0.5</v>
       </c>
       <c r="G18" s="49">
-        <f t="shared" ref="G18:I18" si="24">COUNTIFS($A$2:$A$89,$F$16,$C$2:$C$89,$F18,$D$2:$D$89,G$16)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F18,$D$2:$D$88,G$16)</f>
         <v>0</v>
       </c>
       <c r="H18" s="2">
-        <f t="shared" si="24"/>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F18,$D$2:$D$88,H$16)</f>
         <v>0</v>
       </c>
       <c r="I18" s="50">
-        <f t="shared" si="24"/>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F18,$D$2:$D$88,I$16)</f>
         <v>0</v>
       </c>
       <c r="J18" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K18" s="2"/>
@@ -21911,7 +21898,7 @@
         <v>0.5</v>
       </c>
       <c r="M18" s="49">
-        <f t="shared" ref="M18:M19" si="25">ABS(G$2-$F18)/1</f>
+        <f t="shared" ref="M18:M19" si="20">ABS(G$2-$F18)/1</f>
         <v>0.5</v>
       </c>
       <c r="N18" s="2">
@@ -21927,15 +21914,15 @@
         <v>0.5</v>
       </c>
       <c r="R18" s="49">
-        <f t="shared" ref="R18:T18" si="26">($J18/$J$20) * (G$20/$J$20)</f>
+        <f t="shared" ref="R18:T18" si="21">($J18/$J$20) * (G$20/$J$20)</f>
         <v>0</v>
       </c>
       <c r="S18" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T18" s="50">
-        <f t="shared" si="26"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="U18" s="2"/>
@@ -21971,19 +21958,19 @@
         <v>1</v>
       </c>
       <c r="G19" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$16,$C$2:$C$45,$F19,$D$2:$D$45,G$16)+MAX(C47-D47,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$16,$C$2:$C$44,$F19,$D$2:$D$44,G$16)+MAX(C46-D46,0)</f>
         <v>0</v>
       </c>
       <c r="H19" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$16,$C$2:$C$89,$F19,$D$2:$D$89,H$16)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$16,$C$2:$C$88,$F19,$D$2:$D$88,H$16)</f>
         <v>0</v>
       </c>
       <c r="I19" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$16,$C$2:$C$45,$F19,$D$2:$D$45,I$16) + MIN(C47,D47)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$16,$C$2:$C$44,$F19,$D$2:$D$44,I$16) + MIN(C46,D46)</f>
         <v>9</v>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>9</v>
       </c>
       <c r="K19" s="2"/>
@@ -21991,15 +21978,15 @@
         <v>1</v>
       </c>
       <c r="M19" s="51">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="N19" s="52">
-        <f t="shared" ref="N19:O19" si="27">ABS(H$2-$F19)/1</f>
+        <f t="shared" ref="N19:O19" si="22">ABS(H$2-$F19)/1</f>
         <v>0.5</v>
       </c>
       <c r="O19" s="53">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="P19" s="2"/>
@@ -22007,15 +21994,15 @@
         <v>1</v>
       </c>
       <c r="R19" s="51">
-        <f t="shared" ref="R19:T19" si="28">($J19/$J$20) * (G$20/$J$20)</f>
+        <f t="shared" ref="R19:T19" si="23">($J19/$J$20) * (G$20/$J$20)</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="S19" s="52">
-        <f t="shared" si="28"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T19" s="53">
-        <f t="shared" si="28"/>
+        <f t="shared" si="23"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="U19" s="2"/>
@@ -22051,15 +22038,15 @@
         <v>95</v>
       </c>
       <c r="G20" s="2">
-        <f t="shared" ref="G20:I20" si="29">SUM(G17:G19)</f>
+        <f t="shared" ref="G20:I20" si="24">SUM(G17:G19)</f>
         <v>6</v>
       </c>
       <c r="H20" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="24"/>
         <v>12</v>
       </c>
       <c r="J20" s="2">
@@ -22103,12 +22090,12 @@
         <v>1</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="79" t="s">
+      <c r="F22" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
     </row>
     <row r="23" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="str">
@@ -22200,19 +22187,19 @@
         <v>0</v>
       </c>
       <c r="G24" s="45">
-        <f t="shared" ref="G24:H24" si="30">COUNTIFS($A$2:$A$89,$F$23,$C$2:$C$89,$F24,$D$2:$D$89,G$23)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F24,$D$2:$D$88,G$23)</f>
         <v>1</v>
       </c>
       <c r="H24" s="46">
-        <f t="shared" si="30"/>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F24,$D$2:$D$88,H$23)</f>
         <v>0</v>
       </c>
       <c r="I24" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$23,$C$2:$C$45,$F24,$D$2:$D$45,I$23) + MAX(D50-C50,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$23,$C$2:$C$44,$F24,$D$2:$D$44,I$23) + MAX(D49-C49,0)</f>
         <v>0</v>
       </c>
       <c r="J24" s="2">
-        <f t="shared" ref="J24:J26" si="31">SUM(G24:I24)</f>
+        <f t="shared" ref="J24:J26" si="25">SUM(G24:I24)</f>
         <v>1</v>
       </c>
       <c r="K24" s="2"/>
@@ -22220,15 +22207,15 @@
         <v>0</v>
       </c>
       <c r="M24" s="45">
-        <f t="shared" ref="M24:O24" si="32">ABS(G$2-$F24)/1</f>
+        <f t="shared" ref="M24:O24" si="26">ABS(G$2-$F24)/1</f>
         <v>0</v>
       </c>
       <c r="N24" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="26"/>
         <v>0.5</v>
       </c>
       <c r="O24" s="47">
-        <f t="shared" si="32"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="P24" s="2"/>
@@ -22236,15 +22223,15 @@
         <v>0</v>
       </c>
       <c r="R24" s="45">
-        <f t="shared" ref="R24:T24" si="33">($J24/$J$27) * (G$27/$J$27)</f>
+        <f t="shared" ref="R24:T24" si="27">($J24/$J$27) * (G$27/$J$27)</f>
         <v>0.25</v>
       </c>
       <c r="S24" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T24" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="27"/>
         <v>0.25</v>
       </c>
       <c r="U24" s="2"/>
@@ -22272,27 +22259,27 @@
         <f>'Thermonix Grader #1'!C25</f>
         <v>0.5</v>
       </c>
-      <c r="D25" s="25" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="D25" s="25">
+        <f>'Thermonix Grader #2'!C25</f>
+        <v>0</v>
       </c>
       <c r="F25" s="44">
         <v>0.5</v>
       </c>
       <c r="G25" s="49">
-        <f t="shared" ref="G25:I25" si="34">COUNTIFS($A$2:$A$89,$F$23,$C$2:$C$89,$F25,$D$2:$D$89,G$23)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F25,$D$2:$D$88,G$23)</f>
         <v>0</v>
       </c>
       <c r="H25" s="2">
-        <f t="shared" si="34"/>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F25,$D$2:$D$88,H$23)</f>
         <v>0</v>
       </c>
       <c r="I25" s="50">
-        <f t="shared" si="34"/>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F25,$D$2:$D$88,I$23)</f>
         <v>0</v>
       </c>
       <c r="J25" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="K25" s="2"/>
@@ -22300,7 +22287,7 @@
         <v>0.5</v>
       </c>
       <c r="M25" s="49">
-        <f t="shared" ref="M25:M26" si="35">ABS(G$2-$F25)/1</f>
+        <f t="shared" ref="M25:M26" si="28">ABS(G$2-$F25)/1</f>
         <v>0.5</v>
       </c>
       <c r="N25" s="2">
@@ -22316,15 +22303,15 @@
         <v>0.5</v>
       </c>
       <c r="R25" s="49">
-        <f t="shared" ref="R25:T25" si="36">($J25/$J$27) * (G$27/$J$27)</f>
+        <f t="shared" ref="R25:T25" si="29">($J25/$J$27) * (G$27/$J$27)</f>
         <v>0</v>
       </c>
       <c r="S25" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T25" s="50">
-        <f t="shared" si="36"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="U25" s="2"/>
@@ -22340,39 +22327,39 @@
       </c>
     </row>
     <row r="26" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="3" t="e">
-        <f t="shared" ref="A26:C26" si="37">#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B26" s="4" t="e">
-        <f t="shared" si="37"/>
-        <v>#REF!</v>
-      </c>
-      <c r="C26" s="25" t="e">
-        <f t="shared" si="37"/>
-        <v>#REF!</v>
+      <c r="A26" s="3" t="str">
+        <f>Thermonix!A26</f>
+        <v>Action</v>
+      </c>
+      <c r="B26" s="4" t="str">
+        <f>Thermonix!B26</f>
+        <v>setIngredients()</v>
+      </c>
+      <c r="C26" s="25">
+        <f>'Thermonix Grader #1'!C26</f>
+        <v>0</v>
       </c>
       <c r="D26" s="25">
-        <f>'Thermonix Grader #2'!C25</f>
+        <f>'Thermonix Grader #2'!C26</f>
         <v>0</v>
       </c>
       <c r="F26" s="44">
         <v>1</v>
       </c>
       <c r="G26" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$23,$C$2:$C$45,$F26,$D$2:$D$45,G$23) + MAX(C50-D50,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$23,$C$2:$C$44,$F26,$D$2:$D$44,G$23) + MAX(C49-D49,0)</f>
         <v>0</v>
       </c>
       <c r="H26" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$23,$C$2:$C$89,$F26,$D$2:$D$89,H$23)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$23,$C$2:$C$88,$F26,$D$2:$D$88,H$23)</f>
         <v>0</v>
       </c>
       <c r="I26" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$23,$C$2:$C$45,$F26,$D$2:$D$45,I$23) + MIN(C50,D50)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$23,$C$2:$C$44,$F26,$D$2:$D$44,I$23) + MIN(C49,D49)</f>
         <v>1</v>
       </c>
       <c r="J26" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="K26" s="2"/>
@@ -22380,15 +22367,15 @@
         <v>1</v>
       </c>
       <c r="M26" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="N26" s="52">
-        <f t="shared" ref="N26:O26" si="38">ABS(H$2-$F26)/1</f>
+        <f t="shared" ref="N26:O26" si="30">ABS(H$2-$F26)/1</f>
         <v>0.5</v>
       </c>
       <c r="O26" s="53">
-        <f t="shared" si="38"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="P26" s="2"/>
@@ -22396,15 +22383,15 @@
         <v>1</v>
       </c>
       <c r="R26" s="51">
-        <f t="shared" ref="R26:T26" si="39">($J26/$J$27) * (G$27/$J$27)</f>
+        <f t="shared" ref="R26:T26" si="31">($J26/$J$27) * (G$27/$J$27)</f>
         <v>0.25</v>
       </c>
       <c r="S26" s="52">
-        <f t="shared" si="39"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="T26" s="53">
-        <f t="shared" si="39"/>
+        <f t="shared" si="31"/>
         <v>0.25</v>
       </c>
       <c r="U26" s="2"/>
@@ -22421,34 +22408,34 @@
     </row>
     <row r="27" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="str">
-        <f>Thermonix!A26</f>
-        <v>Action</v>
+        <f>Thermonix!A27</f>
+        <v>Transition</v>
       </c>
       <c r="B27" s="4" t="str">
-        <f>Thermonix!B26</f>
-        <v>setIngredients()</v>
+        <f>Thermonix!B27</f>
+        <v>next (PromptToAdd ⇒ Chop)</v>
       </c>
       <c r="C27" s="25">
-        <f>'Thermonix Grader #1'!C26</f>
+        <f>'Thermonix Grader #1'!C27</f>
         <v>0</v>
       </c>
       <c r="D27" s="25">
-        <f>'Thermonix Grader #2'!C26</f>
-        <v>0</v>
+        <f>'Thermonix Grader #2'!C27</f>
+        <v>1</v>
       </c>
       <c r="F27" s="54" t="s">
         <v>95</v>
       </c>
       <c r="G27" s="2">
-        <f t="shared" ref="G27:I27" si="40">SUM(G24:G26)</f>
+        <f t="shared" ref="G27:I27" si="32">SUM(G24:G26)</f>
         <v>1</v>
       </c>
       <c r="H27" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="J27" s="2">
@@ -22458,62 +22445,62 @@
     </row>
     <row r="28" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="str">
-        <f>Thermonix!A27</f>
-        <v>Transition</v>
+        <f>Thermonix!A28</f>
+        <v>Guard</v>
       </c>
       <c r="B28" s="4" t="str">
-        <f>Thermonix!B27</f>
-        <v>next (PromptToAdd ⇒ Chop)</v>
+        <f>Thermonix!B28</f>
+        <v>[weightCorrect() &amp;&amp; !moreIngredientsRequired()]</v>
       </c>
       <c r="C28" s="25">
-        <f>'Thermonix Grader #1'!C27</f>
+        <f>'Thermonix Grader #1'!C28</f>
         <v>0</v>
       </c>
       <c r="D28" s="25">
-        <f>'Thermonix Grader #2'!C27</f>
+        <f>'Thermonix Grader #2'!C28</f>
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="str">
-        <f>Thermonix!A28</f>
-        <v>Guard</v>
+        <f>Thermonix!A29</f>
+        <v>Action</v>
       </c>
       <c r="B29" s="4" t="str">
-        <f>Thermonix!B28</f>
-        <v>[weightCorrect() &amp;&amp; !moreIngredientsRequired()]</v>
+        <f>Thermonix!B29</f>
+        <v>setChoppingSpeedAndTime()</v>
       </c>
       <c r="C29" s="25">
-        <f>'Thermonix Grader #1'!C28</f>
-        <v>0</v>
+        <f>'Thermonix Grader #1'!C29</f>
+        <v>1</v>
       </c>
       <c r="D29" s="25">
-        <f>'Thermonix Grader #2'!C28</f>
-        <v>1</v>
-      </c>
-      <c r="F29" s="79" t="s">
+        <f>'Thermonix Grader #2'!C29</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="G29" s="80"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
     </row>
     <row r="30" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="str">
-        <f>Thermonix!A29</f>
-        <v>Action</v>
+        <f>Thermonix!A30</f>
+        <v>State</v>
       </c>
       <c r="B30" s="4" t="str">
-        <f>Thermonix!B29</f>
-        <v>setChoppingSpeedAndTime()</v>
+        <f>Thermonix!B30</f>
+        <v>Chop</v>
       </c>
       <c r="C30" s="25">
-        <f>'Thermonix Grader #1'!C29</f>
+        <f>'Thermonix Grader #1'!C30</f>
         <v>1</v>
       </c>
       <c r="D30" s="25">
-        <f>'Thermonix Grader #2'!C29</f>
-        <v>0</v>
+        <f>'Thermonix Grader #2'!C30</f>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>22</v>
@@ -22569,38 +22556,38 @@
     </row>
     <row r="31" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="str">
-        <f>Thermonix!A30</f>
-        <v>State</v>
+        <f>Thermonix!A31</f>
+        <v>Transition</v>
       </c>
       <c r="B31" s="4" t="str">
-        <f>Thermonix!B30</f>
-        <v>Chop</v>
+        <f>Thermonix!B31</f>
+        <v>next (Chop ⇒ PromptToAdd)</v>
       </c>
       <c r="C31" s="25">
-        <f>'Thermonix Grader #1'!C30</f>
-        <v>1</v>
+        <f>'Thermonix Grader #1'!C31</f>
+        <v>0</v>
       </c>
       <c r="D31" s="25">
-        <f>'Thermonix Grader #2'!C30</f>
-        <v>1</v>
+        <f>'Thermonix Grader #2'!C31</f>
+        <v>0</v>
       </c>
       <c r="F31" s="44">
         <v>0</v>
       </c>
       <c r="G31" s="45">
-        <f t="shared" ref="G31:H31" si="41">COUNTIFS($A$2:$A$89,$F$30,$C$2:$C$89,$F31,$D$2:$D$89,G$30)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F31,$D$2:$D$88,G$30)</f>
         <v>4</v>
       </c>
       <c r="H31" s="46">
-        <f t="shared" si="41"/>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F31,$D$2:$D$88,H$30)</f>
         <v>0</v>
       </c>
       <c r="I31" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$30,$C$2:$C$45,$F31,$D$2:$D$45,I$30) + MAX(D48-C48,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$30,$C$2:$C$44,$F31,$D$2:$D$44,I$30) + MAX(D47-C47,0)</f>
         <v>1</v>
       </c>
       <c r="J31" s="2">
-        <f t="shared" ref="J31:J33" si="42">SUM(G31:I31)</f>
+        <f t="shared" ref="J31:J33" si="33">SUM(G31:I31)</f>
         <v>5</v>
       </c>
       <c r="K31" s="2"/>
@@ -22608,15 +22595,15 @@
         <v>0</v>
       </c>
       <c r="M31" s="45">
-        <f t="shared" ref="M31:O31" si="43">ABS(G$2-$F31)/1</f>
+        <f t="shared" ref="M31:O31" si="34">ABS(G$2-$F31)/1</f>
         <v>0</v>
       </c>
       <c r="N31" s="46">
-        <f t="shared" si="43"/>
+        <f t="shared" si="34"/>
         <v>0.5</v>
       </c>
       <c r="O31" s="47">
-        <f t="shared" si="43"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="P31" s="2"/>
@@ -22624,16 +22611,16 @@
         <v>0</v>
       </c>
       <c r="R31" s="45">
-        <f t="shared" ref="R31:T31" si="44">($J31/$J$34) * (G$34/$J$34)</f>
-        <v>0.40816326530612246</v>
+        <f t="shared" ref="R31:T31" si="35">($J31/$J$34) * (G$34/$J$34)</f>
+        <v>0.390625</v>
       </c>
       <c r="S31" s="46">
-        <f t="shared" si="44"/>
-        <v>0.10204081632653061</v>
+        <f t="shared" si="35"/>
+        <v>7.8125E-2</v>
       </c>
       <c r="T31" s="47">
-        <f t="shared" si="44"/>
-        <v>0.20408163265306123</v>
+        <f t="shared" si="35"/>
+        <v>0.15625</v>
       </c>
       <c r="U31" s="2"/>
       <c r="V31" s="48" t="s">
@@ -22641,7 +22628,7 @@
       </c>
       <c r="W31" s="45">
         <f>SUMPRODUCT(G31:I33, M31:O33) /$J$34</f>
-        <v>0.21428571428571427</v>
+        <v>0.25</v>
       </c>
       <c r="X31" s="47" t="s">
         <v>112</v>
@@ -22649,46 +22636,46 @@
     </row>
     <row r="32" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="str">
-        <f>Thermonix!A31</f>
-        <v>Transition</v>
+        <f>Thermonix!A32</f>
+        <v>Guard</v>
       </c>
       <c r="B32" s="4" t="str">
-        <f>Thermonix!B31</f>
-        <v>next (Chop ⇒ PromptToAdd)</v>
+        <f>Thermonix!B32</f>
+        <v>[choppingTimeDone &amp;&amp; moreIngredientsRequired()]</v>
       </c>
       <c r="C32" s="25">
-        <f>'Thermonix Grader #1'!C31</f>
+        <f>'Thermonix Grader #1'!C32</f>
         <v>0</v>
       </c>
       <c r="D32" s="25">
-        <f>'Thermonix Grader #2'!C31</f>
+        <f>'Thermonix Grader #2'!C32</f>
         <v>0</v>
       </c>
       <c r="F32" s="44">
         <v>0.5</v>
       </c>
       <c r="G32" s="49">
-        <f t="shared" ref="G32:I32" si="45">COUNTIFS($A$2:$A$89,$F$30,$C$2:$C$89,$F32,$D$2:$D$89,G$30)</f>
-        <v>0</v>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F32,$D$2:$D$88,G$30)</f>
+        <v>1</v>
       </c>
       <c r="H32" s="2">
-        <f t="shared" si="45"/>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F32,$D$2:$D$88,H$30)</f>
         <v>0</v>
       </c>
       <c r="I32" s="50">
-        <f t="shared" si="45"/>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F32,$D$2:$D$88,I$30)</f>
         <v>0</v>
       </c>
       <c r="J32" s="2">
-        <f t="shared" si="42"/>
-        <v>0</v>
+        <f t="shared" si="33"/>
+        <v>1</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="44">
         <v>0.5</v>
       </c>
       <c r="M32" s="49">
-        <f t="shared" ref="M32:M33" si="46">ABS(G$2-$F32)/1</f>
+        <f t="shared" ref="M32:M33" si="36">ABS(G$2-$F32)/1</f>
         <v>0.5</v>
       </c>
       <c r="N32" s="2">
@@ -22704,16 +22691,16 @@
         <v>0.5</v>
       </c>
       <c r="R32" s="49">
-        <f t="shared" ref="R32:T32" si="47">($J32/$J$34) * (G$34/$J$34)</f>
-        <v>0</v>
+        <f t="shared" ref="R32:T32" si="37">($J32/$J$34) * (G$34/$J$34)</f>
+        <v>7.8125E-2</v>
       </c>
       <c r="S32" s="2">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>1.5625E-2</v>
       </c>
       <c r="T32" s="50">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>3.125E-2</v>
       </c>
       <c r="U32" s="2"/>
       <c r="V32" s="48" t="s">
@@ -22721,7 +22708,7 @@
       </c>
       <c r="W32" s="49">
         <f>SUMPRODUCT(R31:T33, M31:O33)</f>
-        <v>0.43877551020408168</v>
+        <v>0.421875</v>
       </c>
       <c r="X32" s="50" t="s">
         <v>114</v>
@@ -22729,38 +22716,38 @@
     </row>
     <row r="33" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="str">
-        <f>Thermonix!A32</f>
-        <v>Guard</v>
+        <f>Thermonix!A33</f>
+        <v>Action</v>
       </c>
       <c r="B33" s="4" t="str">
-        <f>Thermonix!B32</f>
-        <v>[choppingTimeDone &amp;&amp; moreIngredientsRequired()]</v>
+        <f>Thermonix!B33</f>
+        <v>setIngredients()</v>
       </c>
       <c r="C33" s="25">
-        <f>'Thermonix Grader #1'!C32</f>
+        <f>'Thermonix Grader #1'!C33</f>
         <v>0</v>
       </c>
       <c r="D33" s="25">
-        <f>'Thermonix Grader #2'!C32</f>
+        <f>'Thermonix Grader #2'!C33</f>
         <v>0</v>
       </c>
       <c r="F33" s="44">
         <v>1</v>
       </c>
       <c r="G33" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$30,$C$2:$C$45,$F33,$D$2:$D$45,G$30) + MAX(C48-D48,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$30,$C$2:$C$44,$F33,$D$2:$D$44,G$30) + MAX(C47-D47,0)</f>
         <v>0</v>
       </c>
       <c r="H33" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$30,$C$2:$C$89,$F33,$D$2:$D$89,H$30)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$30,$C$2:$C$88,$F33,$D$2:$D$88,H$30)</f>
         <v>1</v>
       </c>
       <c r="I33" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$30,$C$2:$C$45,$F33,$D$2:$D$45,I$30) + MIN(C48,D48)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$30,$C$2:$C$44,$F33,$D$2:$D$44,I$30) + MIN(C47,D47)</f>
         <v>1</v>
       </c>
       <c r="J33" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="33"/>
         <v>2</v>
       </c>
       <c r="K33" s="2"/>
@@ -22768,15 +22755,15 @@
         <v>1</v>
       </c>
       <c r="M33" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="N33" s="52">
-        <f t="shared" ref="N33:O33" si="48">ABS(H$2-$F33)/1</f>
+        <f t="shared" ref="N33:O33" si="38">ABS(H$2-$F33)/1</f>
         <v>0.5</v>
       </c>
       <c r="O33" s="53">
-        <f t="shared" si="48"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="P33" s="2"/>
@@ -22784,16 +22771,16 @@
         <v>1</v>
       </c>
       <c r="R33" s="51">
-        <f t="shared" ref="R33:T33" si="49">($J33/$J$34) * (G$34/$J$34)</f>
-        <v>0.16326530612244897</v>
+        <f t="shared" ref="R33:T33" si="39">($J33/$J$34) * (G$34/$J$34)</f>
+        <v>0.15625</v>
       </c>
       <c r="S33" s="52">
-        <f t="shared" si="49"/>
-        <v>4.0816326530612242E-2</v>
+        <f t="shared" si="39"/>
+        <v>3.125E-2</v>
       </c>
       <c r="T33" s="53">
-        <f t="shared" si="49"/>
-        <v>8.1632653061224483E-2</v>
+        <f t="shared" si="39"/>
+        <v>6.25E-2</v>
       </c>
       <c r="U33" s="2"/>
       <c r="V33" s="48" t="s">
@@ -22801,7 +22788,7 @@
       </c>
       <c r="W33" s="51">
         <f>1-W31/W32</f>
-        <v>0.51162790697674421</v>
+        <v>0.40740740740740744</v>
       </c>
       <c r="X33" s="53" t="s">
         <v>115</v>
@@ -22809,101 +22796,101 @@
     </row>
     <row r="34" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="str">
-        <f>Thermonix!A33</f>
-        <v>Action</v>
+        <f>Thermonix!A34</f>
+        <v>Transition</v>
       </c>
       <c r="B34" s="4" t="str">
-        <f>Thermonix!B33</f>
-        <v>setIngredients()</v>
+        <f>Thermonix!B34</f>
+        <v>next (Chop ⇒ Cook)</v>
       </c>
       <c r="C34" s="25">
-        <f>'Thermonix Grader #1'!C33</f>
-        <v>0</v>
+        <f>'Thermonix Grader #1'!C34</f>
+        <v>1</v>
       </c>
       <c r="D34" s="25">
-        <f>'Thermonix Grader #2'!C33</f>
-        <v>0</v>
+        <f>'Thermonix Grader #2'!C34</f>
+        <v>1</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="54" t="s">
         <v>95</v>
       </c>
       <c r="G34" s="2">
-        <f t="shared" ref="G34:I34" si="50">SUM(G31:G33)</f>
-        <v>4</v>
+        <f t="shared" ref="G34:I34" si="40">SUM(G31:G33)</f>
+        <v>5</v>
       </c>
       <c r="H34" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="I34" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="40"/>
         <v>2</v>
       </c>
       <c r="J34" s="2">
         <f>SUM(G31:I33)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="str">
-        <f>Thermonix!A34</f>
-        <v>Transition</v>
+        <f>Thermonix!A35</f>
+        <v>Guard</v>
       </c>
       <c r="B35" s="4" t="str">
-        <f>Thermonix!B34</f>
-        <v>next (Chop ⇒ Cook)</v>
+        <f>Thermonix!B35</f>
+        <v>[choppingTimeDone &amp;&amp; !moreIngredientsRequired()]</v>
       </c>
       <c r="C35" s="25">
-        <f>'Thermonix Grader #1'!C34</f>
-        <v>1</v>
+        <f>'Thermonix Grader #1'!C35</f>
+        <v>0</v>
       </c>
       <c r="D35" s="25">
-        <f>'Thermonix Grader #2'!C34</f>
-        <v>1</v>
+        <f>'Thermonix Grader #2'!C35</f>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="str">
-        <f>Thermonix!A35</f>
-        <v>Guard</v>
+        <f>Thermonix!A36</f>
+        <v>Action</v>
       </c>
       <c r="B36" s="4" t="str">
-        <f>Thermonix!B35</f>
-        <v>[choppingTimeDone &amp;&amp; !moreIngredientsRequired()]</v>
+        <f>Thermonix!B36</f>
+        <v>setCookingSpeedAndTime()</v>
       </c>
       <c r="C36" s="25">
-        <f>'Thermonix Grader #1'!C35</f>
-        <v>0</v>
+        <f>'Thermonix Grader #1'!C36</f>
+        <v>1</v>
       </c>
       <c r="D36" s="25">
-        <f>'Thermonix Grader #2'!C35</f>
+        <f>'Thermonix Grader #2'!C36</f>
         <v>0</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="79" t="s">
+      <c r="F36" s="76" t="s">
         <v>104</v>
       </c>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="80"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
     </row>
     <row r="37" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="str">
-        <f>Thermonix!A36</f>
-        <v>Action</v>
+        <f>Thermonix!A37</f>
+        <v>State</v>
       </c>
       <c r="B37" s="4" t="str">
-        <f>Thermonix!B36</f>
-        <v>setCookingSpeedAndTime()</v>
+        <f>Thermonix!B37</f>
+        <v>Cook</v>
       </c>
       <c r="C37" s="25">
-        <f>'Thermonix Grader #1'!C36</f>
+        <f>'Thermonix Grader #1'!C37</f>
         <v>1</v>
       </c>
       <c r="D37" s="25">
-        <f>'Thermonix Grader #2'!C36</f>
-        <v>0</v>
+        <f>'Thermonix Grader #2'!C37</f>
+        <v>1</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="2" t="s">
@@ -22935,16 +22922,16 @@
         <v>85</v>
       </c>
       <c r="P37" s="2"/>
-      <c r="Q37" s="66" t="s">
+      <c r="Q37" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="R37" s="67" t="s">
+      <c r="R37" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="S37" s="67" t="s">
+      <c r="S37" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="T37" s="67" t="s">
+      <c r="T37" s="63" t="s">
         <v>85</v>
       </c>
       <c r="V37" s="43" t="str">
@@ -22960,39 +22947,39 @@
     </row>
     <row r="38" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="str">
-        <f>Thermonix!A37</f>
-        <v>State</v>
+        <f>Thermonix!A38</f>
+        <v>Transition</v>
       </c>
       <c r="B38" s="4" t="str">
-        <f>Thermonix!B37</f>
-        <v>Cook</v>
+        <f>Thermonix!B38</f>
+        <v>after choppingTime (Cook ⇒ PromptToAdd)</v>
       </c>
       <c r="C38" s="25">
-        <f>'Thermonix Grader #1'!C37</f>
-        <v>1</v>
+        <f>'Thermonix Grader #1'!C38</f>
+        <v>0</v>
       </c>
       <c r="D38" s="25">
-        <f>'Thermonix Grader #2'!C37</f>
-        <v>1</v>
+        <f>'Thermonix Grader #2'!C38</f>
+        <v>0</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="44">
         <v>0</v>
       </c>
       <c r="G38" s="45">
-        <f t="shared" ref="G38:H38" si="51">COUNTIFS($A$2:$A$89,$F$37,$C$2:$C$89,$F38,$D$2:$D$89,G$37)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F38,$D$2:$D$88,G$37)</f>
         <v>5</v>
       </c>
       <c r="H38" s="46">
-        <f t="shared" si="51"/>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F38,$D$2:$D$88,H$37)</f>
         <v>0</v>
       </c>
       <c r="I38" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$37,$C$2:$C$45,$F38,$D$2:$D$45,I$37)+MAX(D49-C49,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$37,$C$2:$C$44,$F38,$D$2:$D$44,I$37)+MAX(D48-C48,0)</f>
         <v>0</v>
       </c>
       <c r="J38" s="2">
-        <f t="shared" ref="J38:J40" si="52">SUM(G38:I38)</f>
+        <f t="shared" ref="J38:J40" si="41">SUM(G38:I38)</f>
         <v>5</v>
       </c>
       <c r="K38" s="2"/>
@@ -23000,31 +22987,31 @@
         <v>0</v>
       </c>
       <c r="M38" s="45">
-        <f t="shared" ref="M38:O38" si="53">ABS(G$2-$F38)/1</f>
+        <f t="shared" ref="M38:O38" si="42">ABS(G$2-$F38)/1</f>
         <v>0</v>
       </c>
       <c r="N38" s="46">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>0.5</v>
       </c>
       <c r="O38" s="47">
-        <f t="shared" si="53"/>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="P38" s="2"/>
-      <c r="Q38" s="68">
-        <v>0</v>
-      </c>
-      <c r="R38" s="69">
-        <f t="shared" ref="R38:T38" si="54">($J38/$J$41) * (G$41/$J$41)</f>
+      <c r="Q38" s="64">
+        <v>0</v>
+      </c>
+      <c r="R38" s="65">
+        <f t="shared" ref="R38:T38" si="43">($J38/$J$41) * (G$41/$J$41)</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="S38" s="70">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="T38" s="71">
-        <f t="shared" si="54"/>
+      <c r="S38" s="66">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="67">
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="U38" s="2"/>
@@ -23041,19 +23028,19 @@
     </row>
     <row r="39" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="str">
-        <f>Thermonix!A38</f>
-        <v>Transition</v>
+        <f>Thermonix!A39</f>
+        <v>Guard</v>
       </c>
       <c r="B39" s="4" t="str">
-        <f>Thermonix!B38</f>
-        <v>after choppingTime (Cook ⇒ PromptToAdd)</v>
+        <f>Thermonix!B39</f>
+        <v>[choppingTimeDone &amp;&amp; moreIngredientsRequired()]</v>
       </c>
       <c r="C39" s="25">
-        <f>'Thermonix Grader #1'!C38</f>
+        <f>'Thermonix Grader #1'!C39</f>
         <v>0</v>
       </c>
       <c r="D39" s="25">
-        <f>'Thermonix Grader #2'!C38</f>
+        <f>'Thermonix Grader #2'!C39</f>
         <v>0</v>
       </c>
       <c r="E39" s="5"/>
@@ -23061,19 +23048,19 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="49">
-        <f t="shared" ref="G39:I39" si="55">COUNTIFS($A$2:$A$89,$F$37,$C$2:$C$89,$F39,$D$2:$D$89,G$37)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F39,$D$2:$D$88,G$37)</f>
         <v>0</v>
       </c>
       <c r="H39" s="2">
-        <f t="shared" si="55"/>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F39,$D$2:$D$88,H$37)</f>
         <v>0</v>
       </c>
       <c r="I39" s="50">
-        <f t="shared" si="55"/>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F39,$D$2:$D$88,I$37)</f>
         <v>0</v>
       </c>
       <c r="J39" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K39" s="2"/>
@@ -23081,7 +23068,7 @@
         <v>0.5</v>
       </c>
       <c r="M39" s="49">
-        <f t="shared" ref="M39:M40" si="56">ABS(G$2-$F39)/1</f>
+        <f t="shared" ref="M39:M40" si="44">ABS(G$2-$F39)/1</f>
         <v>0.5</v>
       </c>
       <c r="N39" s="2">
@@ -23093,19 +23080,19 @@
         <v>0.5</v>
       </c>
       <c r="P39" s="2"/>
-      <c r="Q39" s="68">
+      <c r="Q39" s="64">
         <v>0.5</v>
       </c>
-      <c r="R39" s="72">
-        <f t="shared" ref="R39:T39" si="57">($J39/$J$41) * (G$41/$J$41)</f>
-        <v>0</v>
-      </c>
-      <c r="S39" s="66">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="T39" s="73">
-        <f t="shared" si="57"/>
+      <c r="R39" s="68">
+        <f t="shared" ref="R39:T39" si="45">($J39/$J$41) * (G$41/$J$41)</f>
+        <v>0</v>
+      </c>
+      <c r="S39" s="62">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="69">
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="U39" s="2"/>
@@ -23122,19 +23109,19 @@
     </row>
     <row r="40" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="str">
-        <f>Thermonix!A39</f>
-        <v>Guard</v>
+        <f>Thermonix!A40</f>
+        <v>Action</v>
       </c>
       <c r="B40" s="4" t="str">
-        <f>Thermonix!B39</f>
-        <v>[choppingTimeDone &amp;&amp; moreIngredientsRequired()]</v>
+        <f>Thermonix!B40</f>
+        <v>setIngredients()</v>
       </c>
       <c r="C40" s="25">
-        <f>'Thermonix Grader #1'!C39</f>
+        <f>'Thermonix Grader #1'!C40</f>
         <v>0</v>
       </c>
       <c r="D40" s="25">
-        <f>'Thermonix Grader #2'!C39</f>
+        <f>'Thermonix Grader #2'!C40</f>
         <v>0</v>
       </c>
       <c r="E40" s="5"/>
@@ -23142,19 +23129,19 @@
         <v>1</v>
       </c>
       <c r="G40" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$37,$C$2:$C$45,$F40,$D$2:$D$45,G$37)+MAX(C49-D49,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$37,$C$2:$C$44,$F40,$D$2:$D$44,G$37)+MAX(C48-D48,0)</f>
         <v>2</v>
       </c>
       <c r="H40" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$37,$C$2:$C$89,$F40,$D$2:$D$89,H$37)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$37,$C$2:$C$88,$F40,$D$2:$D$88,H$37)</f>
         <v>0</v>
       </c>
       <c r="I40" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$37,$C$2:$C$45,$F40,$D$2:$D$45,I$37) + MIN(C49,D49)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$37,$C$2:$C$44,$F40,$D$2:$D$44,I$37) + MIN(C48,D48)</f>
         <v>0</v>
       </c>
       <c r="J40" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="41"/>
         <v>2</v>
       </c>
       <c r="K40" s="2"/>
@@ -23162,31 +23149,31 @@
         <v>1</v>
       </c>
       <c r="M40" s="51">
-        <f t="shared" si="56"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="N40" s="52">
-        <f t="shared" ref="N40:O40" si="58">ABS(H$2-$F40)/1</f>
+        <f t="shared" ref="N40:O40" si="46">ABS(H$2-$F40)/1</f>
         <v>0.5</v>
       </c>
       <c r="O40" s="53">
-        <f t="shared" si="58"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="P40" s="2"/>
-      <c r="Q40" s="68">
-        <v>1</v>
-      </c>
-      <c r="R40" s="74">
-        <f t="shared" ref="R40:T40" si="59">($J40/$J$41) * (G$41/$J$41)</f>
+      <c r="Q40" s="64">
+        <v>1</v>
+      </c>
+      <c r="R40" s="70">
+        <f t="shared" ref="R40:T40" si="47">($J40/$J$41) * (G$41/$J$41)</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="S40" s="75">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="T40" s="76">
-        <f t="shared" si="59"/>
+      <c r="S40" s="71">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="72">
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="U40" s="2"/>
@@ -23203,35 +23190,35 @@
     </row>
     <row r="41" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="str">
-        <f>Thermonix!A40</f>
-        <v>Action</v>
+        <f>Thermonix!A41</f>
+        <v>Transition</v>
       </c>
       <c r="B41" s="4" t="str">
-        <f>Thermonix!B40</f>
-        <v>setIngredients()</v>
+        <f>Thermonix!B41</f>
+        <v>after cookingTime (Cook ⇒ Ready)</v>
       </c>
       <c r="C41" s="25">
-        <f>'Thermonix Grader #1'!C40</f>
-        <v>0</v>
+        <f>'Thermonix Grader #1'!C41</f>
+        <v>1</v>
       </c>
       <c r="D41" s="25">
-        <f>'Thermonix Grader #2'!C40</f>
-        <v>0</v>
+        <f>'Thermonix Grader #2'!C41</f>
+        <v>1</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="54" t="s">
         <v>95</v>
       </c>
       <c r="G41" s="2">
-        <f t="shared" ref="G41:I41" si="60">SUM(G38:G40)</f>
+        <f t="shared" ref="G41:I41" si="48">SUM(G38:G40)</f>
         <v>7</v>
       </c>
       <c r="H41" s="2">
-        <f t="shared" si="60"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="I41" s="2">
-        <f t="shared" si="60"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="J41" s="2">
@@ -23241,63 +23228,63 @@
     </row>
     <row r="42" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="str">
-        <f>Thermonix!A41</f>
-        <v>Transition</v>
+        <f>Thermonix!A42</f>
+        <v>Guard</v>
       </c>
       <c r="B42" s="4" t="str">
-        <f>Thermonix!B41</f>
-        <v>after cookingTime (Cook ⇒ Ready)</v>
+        <f>Thermonix!B42</f>
+        <v>[!moreIngredientsRequired()]</v>
       </c>
       <c r="C42" s="25">
-        <f>'Thermonix Grader #1'!C41</f>
+        <f>'Thermonix Grader #1'!C42</f>
         <v>1</v>
       </c>
       <c r="D42" s="25">
-        <f>'Thermonix Grader #2'!C41</f>
-        <v>1</v>
+        <f>'Thermonix Grader #2'!C42</f>
+        <v>0.5</v>
       </c>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="str">
-        <f>Thermonix!A42</f>
-        <v>Guard</v>
-      </c>
-      <c r="B43" s="4" t="str">
-        <f>Thermonix!B42</f>
-        <v>[!moreIngredientsRequired()]</v>
-      </c>
-      <c r="C43" s="25">
-        <f>'Thermonix Grader #1'!C42</f>
-        <v>1</v>
-      </c>
-      <c r="D43" s="25">
-        <f>'Thermonix Grader #2'!C42</f>
-        <v>0.5</v>
-      </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="79" t="s">
-        <v>106</v>
-      </c>
-      <c r="G43" s="80"/>
-      <c r="H43" s="80"/>
-      <c r="I43" s="80"/>
-    </row>
-    <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="3" t="str">
         <f>Thermonix!A43</f>
         <v>State</v>
       </c>
-      <c r="B44" s="4" t="str">
+      <c r="B43" s="4" t="str">
         <f>Thermonix!B43</f>
         <v>Ready</v>
       </c>
-      <c r="C44" s="25">
+      <c r="C43" s="25">
         <f>'Thermonix Grader #1'!C43</f>
         <v>1</v>
       </c>
-      <c r="D44" s="25">
+      <c r="D43" s="25">
         <f>'Thermonix Grader #2'!C43</f>
+        <v>1</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
+      <c r="I43" s="77"/>
+    </row>
+    <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="73" t="str">
+        <f>Thermonix!A44</f>
+        <v>Transition</v>
+      </c>
+      <c r="B44" s="74" t="str">
+        <f>Thermonix!B44</f>
+        <v>after 14min 30sec (Ready ⇒ Preparing Shutdown)</v>
+      </c>
+      <c r="C44" s="75">
+        <f>'Thermonix Grader #1'!C44</f>
+        <v>1</v>
+      </c>
+      <c r="D44" s="75">
+        <f>'Thermonix Grader #2'!C44</f>
         <v>1</v>
       </c>
       <c r="E44" s="5"/>
@@ -23355,39 +23342,39 @@
     </row>
     <row r="45" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="str">
-        <f>Thermonix!A44</f>
-        <v>Transition</v>
+        <f>Thermonix!A45</f>
+        <v>State</v>
       </c>
       <c r="B45" s="4" t="str">
-        <f>Thermonix!B44</f>
-        <v>after 14min 30sec (Ready ⇒ Preparing Shutdown)</v>
-      </c>
-      <c r="C45" s="59">
-        <f>'Thermonix Grader #1'!C44</f>
-        <v>1</v>
-      </c>
-      <c r="D45" s="59">
-        <f>'Thermonix Grader #2'!C44</f>
-        <v>1</v>
+        <f>Thermonix!B45</f>
+        <v>additional elements</v>
+      </c>
+      <c r="C45" s="25">
+        <f>'Thermonix Grader #1'!C45</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="25">
+        <f>'Thermonix Grader #2'!C45</f>
+        <v>0</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="44">
         <v>0</v>
       </c>
       <c r="G45" s="45">
-        <f t="shared" ref="G45:H45" si="61">COUNTIFS($A$2:$A$89,$F$44,$C$2:$C$89,$F45,$D$2:$D$89,G$44)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F45,$D$2:$D$88,G$44)</f>
         <v>2</v>
       </c>
       <c r="H45" s="46">
-        <f t="shared" si="61"/>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F45,$D$2:$D$88,H$44)</f>
         <v>0</v>
       </c>
       <c r="I45" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$44,$C$2:$C$45,$F45,$D$2:$D$45,I$44) + MAX(D52-C52,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$44,$C$2:$C$44,$F45,$D$2:$D$44,I$44) + MAX(D51-C51,0)</f>
         <v>0</v>
       </c>
       <c r="J45" s="2">
-        <f t="shared" ref="J45:J47" si="62">SUM(G45:I45)</f>
+        <f t="shared" ref="J45:J47" si="49">SUM(G45:I45)</f>
         <v>2</v>
       </c>
       <c r="K45" s="2"/>
@@ -23395,15 +23382,15 @@
         <v>0</v>
       </c>
       <c r="M45" s="45">
-        <f t="shared" ref="M45:O45" si="63">ABS(G$2-$F45)/1</f>
+        <f t="shared" ref="M45:O45" si="50">ABS(G$2-$F45)/1</f>
         <v>0</v>
       </c>
       <c r="N45" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>0.5</v>
       </c>
       <c r="O45" s="47">
-        <f t="shared" si="63"/>
+        <f t="shared" si="50"/>
         <v>1</v>
       </c>
       <c r="P45" s="2"/>
@@ -23411,15 +23398,15 @@
         <v>0</v>
       </c>
       <c r="R45" s="45">
-        <f t="shared" ref="R45:T45" si="64">($J45/$J$48) * (G$48/$J$48)</f>
+        <f t="shared" ref="R45:T45" si="51">($J45/$J$48) * (G$48/$J$48)</f>
         <v>1</v>
       </c>
       <c r="S45" s="46">
-        <f t="shared" si="64"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="T45" s="47">
-        <f t="shared" si="64"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="U45" s="2"/>
@@ -23435,39 +23422,39 @@
       </c>
     </row>
     <row r="46" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="60" t="str">
-        <f>Thermonix!A45</f>
-        <v>State</v>
-      </c>
-      <c r="B46" s="61" t="str">
-        <f>Thermonix!B45</f>
+      <c r="A46" s="3" t="str">
+        <f>Thermonix!A46</f>
+        <v>Transition</v>
+      </c>
+      <c r="B46" s="4" t="str">
+        <f>Thermonix!B46</f>
         <v>additional elements</v>
       </c>
-      <c r="C46" s="62">
-        <f>'Thermonix Grader #1'!C45</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="62">
-        <f>'Thermonix Grader #2'!C45</f>
+      <c r="C46" s="25">
+        <f>'Thermonix Grader #1'!C46</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="25">
+        <f>'Thermonix Grader #2'!C46</f>
         <v>0</v>
       </c>
       <c r="F46" s="44">
         <v>0.5</v>
       </c>
       <c r="G46" s="49">
-        <f t="shared" ref="G46:I46" si="65">COUNTIFS($A$2:$A$89,$F$44,$C$2:$C$89,$F46,$D$2:$D$89,G$44)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F46,$D$2:$D$88,G$44)</f>
         <v>0</v>
       </c>
       <c r="H46" s="2">
-        <f t="shared" si="65"/>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F46,$D$2:$D$88,H$44)</f>
         <v>0</v>
       </c>
       <c r="I46" s="50">
-        <f t="shared" si="65"/>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F46,$D$2:$D$88,I$44)</f>
         <v>0</v>
       </c>
       <c r="J46" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="K46" s="2"/>
@@ -23475,7 +23462,7 @@
         <v>0.5</v>
       </c>
       <c r="M46" s="49">
-        <f t="shared" ref="M46:M47" si="66">ABS(G$2-$F46)/1</f>
+        <f t="shared" ref="M46:M47" si="52">ABS(G$2-$F46)/1</f>
         <v>0.5</v>
       </c>
       <c r="N46" s="2">
@@ -23491,15 +23478,15 @@
         <v>0.5</v>
       </c>
       <c r="R46" s="49">
-        <f t="shared" ref="R46:T46" si="67">($J46/$J$48) * (G$48/$J$48)</f>
+        <f t="shared" ref="R46:T46" si="53">($J46/$J$48) * (G$48/$J$48)</f>
         <v>0</v>
       </c>
       <c r="S46" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="T46" s="50">
-        <f t="shared" si="67"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="U46" s="2"/>
@@ -23516,38 +23503,38 @@
     </row>
     <row r="47" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="str">
-        <f>Thermonix!A46</f>
-        <v>Transition</v>
+        <f>Thermonix!A47</f>
+        <v>Guard</v>
       </c>
       <c r="B47" s="4" t="str">
-        <f>Thermonix!B46</f>
+        <f>Thermonix!B47</f>
         <v>additional elements</v>
       </c>
       <c r="C47" s="25">
-        <f>'Thermonix Grader #1'!C46</f>
+        <f>'Thermonix Grader #1'!C47</f>
         <v>0</v>
       </c>
       <c r="D47" s="25">
-        <f>'Thermonix Grader #2'!C46</f>
+        <f>'Thermonix Grader #2'!C47</f>
         <v>0</v>
       </c>
       <c r="F47" s="44">
         <v>1</v>
       </c>
       <c r="G47" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$44,$C$2:$C$45,$F47,$D$2:$D$45,G$44) + MAX(C52-D52,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$44,$C$2:$C$44,$F47,$D$2:$D$44,G$44) + MAX(C51-D51,0)</f>
         <v>0</v>
       </c>
       <c r="H47" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$44,$C$2:$C$89,$F47,$D$2:$D$89,H$44)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$44,$C$2:$C$88,$F47,$D$2:$D$88,H$44)</f>
         <v>0</v>
       </c>
       <c r="I47" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$44,$C$2:$C$45,$F47,$D$2:$D$45,I$44) + MIN(C52,D52)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$44,$C$2:$C$44,$F47,$D$2:$D$44,I$44) + MIN(C51,D51)</f>
         <v>0</v>
       </c>
       <c r="J47" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="K47" s="2"/>
@@ -23555,15 +23542,15 @@
         <v>1</v>
       </c>
       <c r="M47" s="51">
-        <f t="shared" si="66"/>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="N47" s="52">
-        <f t="shared" ref="N47:O47" si="68">ABS(H$2-$F47)/1</f>
+        <f t="shared" ref="N47:O47" si="54">ABS(H$2-$F47)/1</f>
         <v>0.5</v>
       </c>
       <c r="O47" s="53">
-        <f t="shared" si="68"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="P47" s="2"/>
@@ -23571,15 +23558,15 @@
         <v>1</v>
       </c>
       <c r="R47" s="51">
-        <f t="shared" ref="R47:T47" si="69">($J47/$J$48) * (G$48/$J$48)</f>
+        <f t="shared" ref="R47:T47" si="55">($J47/$J$48) * (G$48/$J$48)</f>
         <v>0</v>
       </c>
       <c r="S47" s="52">
-        <f t="shared" si="69"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="T47" s="53">
-        <f t="shared" si="69"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="U47" s="2"/>
@@ -23596,34 +23583,34 @@
     </row>
     <row r="48" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="str">
-        <f>Thermonix!A47</f>
-        <v>Guard</v>
+        <f>Thermonix!A48</f>
+        <v>Action</v>
       </c>
       <c r="B48" s="4" t="str">
-        <f>Thermonix!B47</f>
+        <f>Thermonix!B48</f>
         <v>additional elements</v>
       </c>
       <c r="C48" s="25">
-        <f>'Thermonix Grader #1'!C47</f>
+        <f>'Thermonix Grader #1'!C48</f>
         <v>0</v>
       </c>
       <c r="D48" s="25">
-        <f>'Thermonix Grader #2'!C47</f>
+        <f>'Thermonix Grader #2'!C48</f>
         <v>0</v>
       </c>
       <c r="F48" s="54" t="s">
         <v>95</v>
       </c>
       <c r="G48" s="2">
-        <f t="shared" ref="G48:I48" si="70">SUM(G45:G47)</f>
+        <f t="shared" ref="G48:I48" si="56">SUM(G45:G47)</f>
         <v>2</v>
       </c>
       <c r="H48" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="I48" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="J48" s="2">
@@ -23633,61 +23620,61 @@
     </row>
     <row r="49" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="3" t="str">
-        <f>Thermonix!A48</f>
-        <v>Action</v>
+        <f>Thermonix!A49</f>
+        <v>Composite State</v>
       </c>
       <c r="B49" s="4" t="str">
-        <f>Thermonix!B48</f>
+        <f>Thermonix!B49</f>
         <v>additional elements</v>
       </c>
       <c r="C49" s="25">
-        <f>'Thermonix Grader #1'!C48</f>
+        <f>'Thermonix Grader #1'!C49</f>
         <v>0</v>
       </c>
       <c r="D49" s="25">
-        <f>'Thermonix Grader #2'!C48</f>
+        <f>'Thermonix Grader #2'!C49</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="str">
-        <f>Thermonix!A49</f>
-        <v>Composite State</v>
+        <f>Thermonix!A50</f>
+        <v>Region</v>
       </c>
       <c r="B50" s="4" t="str">
-        <f>Thermonix!B49</f>
+        <f>Thermonix!B50</f>
         <v>additional elements</v>
       </c>
       <c r="C50" s="25">
-        <f>'Thermonix Grader #1'!C49</f>
+        <f>'Thermonix Grader #1'!C50</f>
         <v>0</v>
       </c>
       <c r="D50" s="25">
-        <f>'Thermonix Grader #2'!C49</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="79" t="s">
+        <f>'Thermonix Grader #2'!C50</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="76" t="s">
         <v>108</v>
       </c>
-      <c r="G50" s="80"/>
-      <c r="H50" s="80"/>
-      <c r="I50" s="80"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="77"/>
+      <c r="I50" s="77"/>
     </row>
     <row r="51" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="str">
-        <f>Thermonix!A50</f>
-        <v>Region</v>
+        <f>Thermonix!A51</f>
+        <v>History State</v>
       </c>
       <c r="B51" s="4" t="str">
-        <f>Thermonix!B50</f>
+        <f>Thermonix!B51</f>
         <v>additional elements</v>
       </c>
       <c r="C51" s="25">
-        <f>'Thermonix Grader #1'!C50</f>
+        <f>'Thermonix Grader #1'!C51</f>
         <v>0</v>
       </c>
       <c r="D51" s="25">
-        <f>'Thermonix Grader #2'!C50</f>
+        <f>'Thermonix Grader #2'!C51</f>
         <v>0</v>
       </c>
       <c r="F51" s="2" t="s">
@@ -23743,39 +23730,27 @@
       </c>
     </row>
     <row r="52" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="3" t="str">
-        <f>Thermonix!A51</f>
-        <v>History State</v>
-      </c>
-      <c r="B52" s="4" t="str">
-        <f>Thermonix!B51</f>
-        <v>additional elements</v>
-      </c>
-      <c r="C52" s="25">
-        <f>'Thermonix Grader #1'!C51</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="25">
-        <f>'Thermonix Grader #2'!C51</f>
-        <v>0</v>
-      </c>
+      <c r="A52" s="3"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
       <c r="F52" s="44">
         <v>0</v>
       </c>
       <c r="G52" s="45">
-        <f t="shared" ref="G52:H52" si="71">COUNTIFS($A$2:$A$89,$F$51,$C$2:$C$89,$F52,$D$2:$D$89,G$51)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F52,$D$2:$D$88,G$51)</f>
         <v>1</v>
       </c>
       <c r="H52" s="46">
-        <f t="shared" si="71"/>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F52,$D$2:$D$88,H$51)</f>
         <v>0</v>
       </c>
       <c r="I52" s="47">
-        <f>COUNTIFS($A$2:$A$45,$F$51,$C$2:$C$45,$F52,$D$2:$D$45,I$51)+MAX(D51-C51,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$51,$C$2:$C$44,$F52,$D$2:$D$44,I$51)+MAX(D50-C50,0)</f>
         <v>0</v>
       </c>
       <c r="J52" s="2">
-        <f t="shared" ref="J52:J54" si="72">SUM(G52:I52)</f>
+        <f t="shared" ref="J52:J54" si="57">SUM(G52:I52)</f>
         <v>1</v>
       </c>
       <c r="K52" s="2"/>
@@ -23783,15 +23758,15 @@
         <v>0</v>
       </c>
       <c r="M52" s="45">
-        <f t="shared" ref="M52:O52" si="73">ABS(G$2-$F52)/1</f>
+        <f t="shared" ref="M52:O52" si="58">ABS(G$2-$F52)/1</f>
         <v>0</v>
       </c>
       <c r="N52" s="46">
-        <f t="shared" si="73"/>
+        <f t="shared" si="58"/>
         <v>0.5</v>
       </c>
       <c r="O52" s="47">
-        <f t="shared" si="73"/>
+        <f t="shared" si="58"/>
         <v>1</v>
       </c>
       <c r="P52" s="2"/>
@@ -23799,15 +23774,15 @@
         <v>0</v>
       </c>
       <c r="R52" s="45">
-        <f t="shared" ref="R52:T52" si="74">($J52/$J$55) * (G$55/$J$55)</f>
+        <f t="shared" ref="R52:T52" si="59">($J52/$J$55) * (G$55/$J$55)</f>
         <v>1</v>
       </c>
       <c r="S52" s="46">
-        <f t="shared" si="74"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="T52" s="47">
-        <f t="shared" si="74"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="U52" s="2"/>
@@ -23831,19 +23806,19 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="49">
-        <f t="shared" ref="G53:I53" si="75">COUNTIFS($A$2:$A$89,$F$51,$C$2:$C$89,$F53,$D$2:$D$89,G$51)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F53,$D$2:$D$88,G$51)</f>
         <v>0</v>
       </c>
       <c r="H53" s="2">
-        <f t="shared" si="75"/>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F53,$D$2:$D$88,H$51)</f>
         <v>0</v>
       </c>
       <c r="I53" s="50">
-        <f t="shared" si="75"/>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F53,$D$2:$D$88,I$51)</f>
         <v>0</v>
       </c>
       <c r="J53" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="K53" s="2"/>
@@ -23851,7 +23826,7 @@
         <v>0.5</v>
       </c>
       <c r="M53" s="49">
-        <f t="shared" ref="M53:M54" si="76">ABS(G$2-$F53)/1</f>
+        <f t="shared" ref="M53:M54" si="60">ABS(G$2-$F53)/1</f>
         <v>0.5</v>
       </c>
       <c r="N53" s="2">
@@ -23867,15 +23842,15 @@
         <v>0.5</v>
       </c>
       <c r="R53" s="49">
-        <f t="shared" ref="R53:T53" si="77">($J53/$J$55) * (G$55/$J$55)</f>
+        <f t="shared" ref="R53:T53" si="61">($J53/$J$55) * (G$55/$J$55)</f>
         <v>0</v>
       </c>
       <c r="S53" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="T53" s="50">
-        <f t="shared" si="77"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="U53" s="2"/>
@@ -23899,19 +23874,19 @@
         <v>1</v>
       </c>
       <c r="G54" s="51">
-        <f>COUNTIFS($A$2:$A$45,$F$51,$C$2:$C$45,$F54,$D$2:$D$45,G$51) + MAX(C51-D51,0)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$51,$C$2:$C$44,$F54,$D$2:$D$44,G$51) + MAX(C50-D50,0)</f>
         <v>0</v>
       </c>
       <c r="H54" s="52">
-        <f>COUNTIFS($A$2:$A$89,$F$51,$C$2:$C$89,$F54,$D$2:$D$89,H$51)</f>
+        <f>COUNTIFS($A$2:$A$88,$F$51,$C$2:$C$88,$F54,$D$2:$D$88,H$51)</f>
         <v>0</v>
       </c>
       <c r="I54" s="53">
-        <f>COUNTIFS($A$2:$A$45,$F$51,$C$2:$C$45,$F54,$D$2:$D$45,I$51)+MIN(C51,D51)</f>
+        <f>COUNTIFS($A$2:$A$44,$F$51,$C$2:$C$44,$F54,$D$2:$D$44,I$51)+MIN(C50,D50)</f>
         <v>0</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="K54" s="2"/>
@@ -23919,15 +23894,15 @@
         <v>1</v>
       </c>
       <c r="M54" s="51">
-        <f t="shared" si="76"/>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="N54" s="52">
-        <f t="shared" ref="N54:O54" si="78">ABS(H$2-$F54)/1</f>
+        <f t="shared" ref="N54:O54" si="62">ABS(H$2-$F54)/1</f>
         <v>0.5</v>
       </c>
       <c r="O54" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="P54" s="2"/>
@@ -23935,15 +23910,15 @@
         <v>1</v>
       </c>
       <c r="R54" s="51">
-        <f t="shared" ref="R54:T54" si="79">($J54/$J$55) * (G$55/$J$55)</f>
+        <f t="shared" ref="R54:T54" si="63">($J54/$J$55) * (G$55/$J$55)</f>
         <v>0</v>
       </c>
       <c r="S54" s="52">
-        <f t="shared" si="79"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="T54" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="U54" s="2"/>
@@ -23967,15 +23942,15 @@
         <v>95</v>
       </c>
       <c r="G55" s="2">
-        <f t="shared" ref="G55:I55" si="80">SUM(G52:G54)</f>
+        <f t="shared" ref="G55:I55" si="64">SUM(G52:G54)</f>
         <v>1</v>
       </c>
       <c r="H55" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="I55" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="J55" s="2">
@@ -24102,7 +24077,6 @@
     <row r="75" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3"/>
       <c r="B75" s="4"/>
-      <c r="C75" s="5"/>
       <c r="D75" s="5"/>
     </row>
     <row r="76" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24148,11 +24122,10 @@
     <row r="84" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="3"/>
       <c r="B84" s="4"/>
-      <c r="D84" s="5"/>
     </row>
     <row r="85" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="3"/>
-      <c r="B85" s="4"/>
+      <c r="A85" s="1"/>
+      <c r="B85" s="2"/>
     </row>
     <row r="86" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="1"/>
@@ -24890,10 +24863,7 @@
       <c r="A269" s="1"/>
       <c r="B269" s="2"/>
     </row>
-    <row r="270" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A270" s="1"/>
-      <c r="B270" s="2"/>
-    </row>
+    <row r="270" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="271" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="272" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
